--- a/base_dados/base-dados-pesquisa/2023/ibovespa_magic_formula_2023.xlsx
+++ b/base_dados/base-dados-pesquisa/2023/ibovespa_magic_formula_2023.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="152">
   <si>
     <t>ativo</t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t>ROA</t>
+  </si>
+  <si>
+    <t>giro_ativo</t>
+  </si>
+  <si>
+    <t>alavancagem</t>
   </si>
   <si>
     <t>AXIA ENERGIA S.A.</t>
@@ -821,10 +827,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P196"/>
+  <dimension ref="A1:R196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -873,16 +879,22 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D2">
         <v>22.10003089904785</v>
@@ -923,16 +935,22 @@
       <c r="P2">
         <v>0.002399156096165026</v>
       </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2">
+        <v>0.05442817938238664</v>
+      </c>
+      <c r="R2">
+        <v>0.1511685111682828</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D3">
         <v>28.52345848083496</v>
@@ -973,25 +991,31 @@
       <c r="P3">
         <v>0.009807244118204836</v>
       </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="Q3">
+        <v>0.05600898491336506</v>
+      </c>
+      <c r="R3">
+        <v>0.1479517349568082</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D4">
-        <v>25.8517894744873</v>
+        <v>25.85178565979004</v>
       </c>
       <c r="E4">
         <v>2253882</v>
       </c>
       <c r="F4">
-        <v>58266882.9643364</v>
+        <v>58266874.36645889</v>
       </c>
       <c r="G4">
         <v>3890393</v>
@@ -1003,13 +1027,13 @@
         <v>113118115</v>
       </c>
       <c r="J4">
-        <v>78875555.9643364</v>
+        <v>78875547.36645889</v>
       </c>
       <c r="K4">
         <v>0.02909209933315679</v>
       </c>
       <c r="L4">
-        <v>0.04932317690108001</v>
+        <v>0.04932318227758321</v>
       </c>
       <c r="M4">
         <v>0.0130534972227923</v>
@@ -1023,25 +1047,31 @@
       <c r="P4">
         <v>0.00866045479530073</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4">
+        <v>0.05150470480445628</v>
+      </c>
+      <c r="R4">
+        <v>0.1856453979523985</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D5">
-        <v>31.91685485839844</v>
+        <v>31.9168529510498</v>
       </c>
       <c r="E5">
         <v>2039086540</v>
       </c>
       <c r="F5">
-        <v>65081229140.89386</v>
+        <v>65081225251.64494</v>
       </c>
       <c r="G5">
         <v>1490030</v>
@@ -1053,13 +1083,13 @@
         <v>11349991</v>
       </c>
       <c r="J5">
-        <v>65087595014.89386</v>
+        <v>65087591125.64494</v>
       </c>
       <c r="K5">
         <v>0.08410709835506197</v>
       </c>
       <c r="L5">
-        <v>2.289268791785961E-05</v>
+        <v>2.289268928579104E-05</v>
       </c>
       <c r="M5">
         <v>0.04484558622116969</v>
@@ -1073,16 +1103,22 @@
       <c r="P5">
         <v>0.02676101109058545</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5">
+        <v>0.343874289593491</v>
+      </c>
+      <c r="R5">
+        <v>0.356361292813664</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D6">
         <v>39.8762092590332</v>
@@ -1123,25 +1159,31 @@
       <c r="P6">
         <v>0.03113296645855858</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6">
+        <v>0.3122268930947917</v>
+      </c>
+      <c r="R6">
+        <v>0.3940397118666743</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D7">
-        <v>37.68171310424805</v>
+        <v>37.68171691894531</v>
       </c>
       <c r="E7">
         <v>2035314165</v>
       </c>
       <c r="F7">
-        <v>76694124442.54218</v>
+        <v>76694132206.64955</v>
       </c>
       <c r="G7">
         <v>1623978</v>
@@ -1153,13 +1195,13 @@
         <v>12044962</v>
       </c>
       <c r="J7">
-        <v>76702451533.54218</v>
+        <v>76702459297.64955</v>
       </c>
       <c r="K7">
         <v>0.07971597167943752</v>
       </c>
       <c r="L7">
-        <v>2.117243930971138E-05</v>
+        <v>2.117243716655855E-05</v>
       </c>
       <c r="M7">
         <v>0.05717668515683155</v>
@@ -1173,25 +1215,31 @@
       <c r="P7">
         <v>0.03213283037432461</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7">
+        <v>0.3419630107889709</v>
+      </c>
+      <c r="R7">
+        <v>0.3894450087968681</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D8">
-        <v>19.85773658752441</v>
+        <v>19.85774040222168</v>
       </c>
       <c r="E8">
         <v>640131</v>
       </c>
       <c r="F8">
-        <v>12711552.77950859</v>
+        <v>12711555.22141457</v>
       </c>
       <c r="G8">
         <v>422088</v>
@@ -1203,13 +1251,13 @@
         <v>10815117</v>
       </c>
       <c r="J8">
-        <v>12589129.77950859</v>
+        <v>12589132.22141457</v>
       </c>
       <c r="K8">
         <v>0.03947442992383397</v>
       </c>
       <c r="L8">
-        <v>0.03352797273462343</v>
+        <v>0.03352796623122388</v>
       </c>
       <c r="M8">
         <v>0.03286843776169966</v>
@@ -1223,16 +1271,22 @@
       <c r="P8">
         <v>0.02851403225744351</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8">
+        <v>0.6104493216490903</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D9">
         <v>24.239990234375</v>
@@ -1273,16 +1327,22 @@
       <c r="P9">
         <v>0.05494147520595506</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9">
+        <v>0.624331876767303</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D10">
         <v>22.87614250183105</v>
@@ -1323,16 +1383,22 @@
       <c r="P10">
         <v>0.04347417743742327</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10">
+        <v>0.6332113225684848</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D11">
         <v>17.79687881469727</v>
@@ -1373,16 +1439,22 @@
       <c r="P11">
         <v>0.002988895323707805</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11">
+        <v>0.1002873119067045</v>
+      </c>
+      <c r="R11">
+        <v>0.2193642857004628</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D12">
         <v>21.03162002563477</v>
@@ -1423,16 +1495,22 @@
       <c r="P12">
         <v>0.006903827366741623</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12">
+        <v>0.1140898329145116</v>
+      </c>
+      <c r="R12">
+        <v>0.2268794743244281</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D13">
         <v>21.61898803710938</v>
@@ -1473,16 +1551,22 @@
       <c r="P13">
         <v>0.01836082882166274</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13">
+        <v>0.1207941615627694</v>
+      </c>
+      <c r="R13">
+        <v>0.2610578079594433</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D14">
         <v>9.072550773620605</v>
@@ -1523,16 +1607,22 @@
       <c r="P14">
         <v>0.007714062638407082</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14">
+        <v>0.1054915404094815</v>
+      </c>
+      <c r="R14">
+        <v>0.09258423829120969</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D15">
         <v>11.66469669342041</v>
@@ -1573,25 +1663,31 @@
       <c r="P15">
         <v>0.01124591877419787</v>
       </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15">
+        <v>0.1052525024454459</v>
+      </c>
+      <c r="R15">
+        <v>0.08597857751492287</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D16">
-        <v>12.0194149017334</v>
+        <v>12.01941299438477</v>
       </c>
       <c r="E16">
         <v>2420599036</v>
       </c>
       <c r="F16">
-        <v>29094184124.4199</v>
+        <v>29094179507.49364</v>
       </c>
       <c r="G16">
         <v>1218872</v>
@@ -1603,13 +1699,13 @@
         <v>25574058</v>
       </c>
       <c r="J16">
-        <v>29095412379.4199</v>
+        <v>29095407762.49364</v>
       </c>
       <c r="K16">
         <v>0.04547637362491812</v>
       </c>
       <c r="L16">
-        <v>4.189224005850993E-05</v>
+        <v>4.189224670606699E-05</v>
       </c>
       <c r="M16">
         <v>0.02799731665580801</v>
@@ -1623,16 +1719,22 @@
       <c r="P16">
         <v>0.01279197867070366</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16">
+        <v>0.1081829198012676</v>
+      </c>
+      <c r="R16">
+        <v>0.08641791313295935</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D17">
         <v>26.84604072570801</v>
@@ -1673,16 +1775,22 @@
       <c r="P17">
         <v>0.08613019375751961</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17">
+        <v>0.5133994563598148</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D18">
         <v>31.14588356018066</v>
@@ -1723,16 +1831,22 @@
       <c r="P18">
         <v>0.06655597418105245</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18">
+        <v>0.5011327761133103</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D19">
         <v>31.13189506530762</v>
@@ -1773,25 +1887,31 @@
       <c r="P19">
         <v>0.06569374480814216</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19">
+        <v>0.4991976032039621</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D20">
-        <v>23.70475196838379</v>
+        <v>23.70475006103516</v>
       </c>
       <c r="E20">
         <v>815927740</v>
       </c>
       <c r="F20">
-        <v>19341364700.82394</v>
+        <v>19341363144.56528</v>
       </c>
       <c r="G20">
         <v>1836760</v>
@@ -1803,13 +1923,13 @@
         <v>9244143</v>
       </c>
       <c r="J20">
-        <v>19346747078.82394</v>
+        <v>19346745522.56528</v>
       </c>
       <c r="K20">
         <v>0.1255773673042277</v>
       </c>
       <c r="L20">
-        <v>9.493895756824326E-05</v>
+        <v>9.493896520516466E-05</v>
       </c>
       <c r="M20">
         <v>0.09543578025567108</v>
@@ -1823,16 +1943,22 @@
       <c r="P20">
         <v>0.03836665456377197</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20">
+        <v>0.1267150025751811</v>
+      </c>
+      <c r="R20">
+        <v>0.2759031192634377</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D21">
         <v>28.11649131774902</v>
@@ -1873,25 +1999,31 @@
       <c r="P21">
         <v>0.03056519738977732</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21">
+        <v>0.1088670382520017</v>
+      </c>
+      <c r="R21">
+        <v>0.2734961989217398</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D22">
-        <v>26.08025932312012</v>
+        <v>26.08026313781738</v>
       </c>
       <c r="E22">
         <v>815927740</v>
       </c>
       <c r="F22">
-        <v>21279607048.12733</v>
+        <v>21279610160.64465</v>
       </c>
       <c r="G22">
         <v>1475128</v>
@@ -1903,13 +2035,13 @@
         <v>8436831</v>
       </c>
       <c r="J22">
-        <v>21285453086.12733</v>
+        <v>21285456198.64465</v>
       </c>
       <c r="K22">
         <v>0.1032795301840267</v>
       </c>
       <c r="L22">
-        <v>6.930216585154141E-05</v>
+        <v>6.930215571766457E-05</v>
       </c>
       <c r="M22">
         <v>0.1027210335255026</v>
@@ -1923,25 +2055,31 @@
       <c r="P22">
         <v>0.03745191943896105</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22">
+        <v>0.1086216294342078</v>
+      </c>
+      <c r="R22">
+        <v>0.2759852185401867</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D23">
-        <v>15.68352508544922</v>
+        <v>15.68352317810059</v>
       </c>
       <c r="E23">
         <v>1661644031</v>
       </c>
       <c r="F23">
-        <v>26060435843.27546</v>
+        <v>26060432673.94099</v>
       </c>
       <c r="G23">
         <v>1675885</v>
@@ -1953,13 +2091,13 @@
         <v>68768198</v>
       </c>
       <c r="J23">
-        <v>26074420156.27546</v>
+        <v>26074416986.94099</v>
       </c>
       <c r="K23">
         <v>0.02025177217885268</v>
       </c>
       <c r="L23">
-        <v>6.427314547958054E-05</v>
+        <v>6.427315329195449E-05</v>
       </c>
       <c r="M23">
         <v>0.01213624937503815</v>
@@ -1973,25 +2111,31 @@
       <c r="P23">
         <v>0.006894167953118786</v>
       </c>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="Q23">
+        <v>0.105081896764042</v>
+      </c>
+      <c r="R23">
+        <v>0.1560554773890467</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D24">
-        <v>17.93721961975098</v>
+        <v>17.93722152709961</v>
       </c>
       <c r="E24">
         <v>1658276931</v>
       </c>
       <c r="F24">
-        <v>29744877501.71364</v>
+        <v>29744880664.62587</v>
       </c>
       <c r="G24">
         <v>1872454</v>
@@ -2003,13 +2147,13 @@
         <v>68651381</v>
       </c>
       <c r="J24">
-        <v>29758036733.71364</v>
+        <v>29758039896.62587</v>
       </c>
       <c r="K24">
         <v>0.02288766617602535</v>
       </c>
       <c r="L24">
-        <v>6.292263218690933E-05</v>
+        <v>6.292262549901039E-05</v>
       </c>
       <c r="M24">
         <v>0.01632865914234121</v>
@@ -2023,25 +2167,31 @@
       <c r="P24">
         <v>0.009405627852603163</v>
       </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="Q24">
+        <v>0.1068338313264593</v>
+      </c>
+      <c r="R24">
+        <v>0.1525393168895587</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C25" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D25">
-        <v>18.12424850463867</v>
+        <v>18.12425422668457</v>
       </c>
       <c r="E25">
         <v>1656556432</v>
       </c>
       <c r="F25">
-        <v>30023840435.52557</v>
+        <v>30023849914.41751</v>
       </c>
       <c r="G25">
         <v>2118012</v>
@@ -2053,13 +2203,13 @@
         <v>69269931</v>
       </c>
       <c r="J25">
-        <v>30037254313.52557</v>
+        <v>30037263792.41751</v>
       </c>
       <c r="K25">
         <v>0.02561580103306562</v>
       </c>
       <c r="L25">
-        <v>7.05128364228109E-05</v>
+        <v>7.051281417099858E-05</v>
       </c>
       <c r="M25">
         <v>0.02131672399096226</v>
@@ -2073,25 +2223,31 @@
       <c r="P25">
         <v>0.01240224018218209</v>
       </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="Q25">
+        <v>0.1101279196876735</v>
+      </c>
+      <c r="R25">
+        <v>0.1482354566064589</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D26">
-        <v>1.589640855789185</v>
+        <v>1.589640974998474</v>
       </c>
       <c r="E26">
         <v>1867836812</v>
       </c>
       <c r="F26">
-        <v>2969189708.302222</v>
+        <v>2969189930.965722</v>
       </c>
       <c r="G26">
         <v>259729</v>
@@ -2103,13 +2259,13 @@
         <v>12220694</v>
       </c>
       <c r="J26">
-        <v>2972350500.302222</v>
+        <v>2972350722.965722</v>
       </c>
       <c r="K26">
         <v>0.01688581974459425</v>
       </c>
       <c r="L26">
-        <v>8.738168663944286E-05</v>
+        <v>8.738168009354235E-05</v>
       </c>
       <c r="M26">
         <v>0.004411860733932132</v>
@@ -2123,16 +2279,22 @@
       <c r="P26">
         <v>0.003268602483291577</v>
       </c>
-    </row>
-    <row r="27" spans="1:16">
+      <c r="Q26">
+        <v>0.08062237547425381</v>
+      </c>
+      <c r="R26">
+        <v>0.2040317613878963</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D27">
         <v>2.771245002746582</v>
@@ -2173,25 +2335,31 @@
       <c r="P27">
         <v>-0.003921897519966439</v>
       </c>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="Q27">
+        <v>0.08378765136725624</v>
+      </c>
+      <c r="R27">
+        <v>0.2106283803458112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D28">
-        <v>2.261199474334717</v>
+        <v>2.261199712753296</v>
       </c>
       <c r="E28">
         <v>1871916288</v>
       </c>
       <c r="F28">
-        <v>4232776126.424194</v>
+        <v>4232776572.723816</v>
       </c>
       <c r="G28">
         <v>90916</v>
@@ -2203,13 +2371,13 @@
         <v>12083346</v>
       </c>
       <c r="J28">
-        <v>4235862474.424194</v>
+        <v>4235862920.723816</v>
       </c>
       <c r="K28">
         <v>0.005993265256372344</v>
       </c>
       <c r="L28">
-        <v>2.14633974896361E-05</v>
+        <v>2.146339522820641E-05</v>
       </c>
       <c r="M28">
         <v>-0.009654279534824211</v>
@@ -2223,16 +2391,22 @@
       <c r="P28">
         <v>-0.007218973593344108</v>
       </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="Q28">
+        <v>0.07859334472715292</v>
+      </c>
+      <c r="R28">
+        <v>0.1977159389337806</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E29">
         <v>2019998000</v>
@@ -2261,16 +2435,22 @@
       <c r="P29">
         <v>0.02911215139417114</v>
       </c>
-    </row>
-    <row r="30" spans="1:16">
+      <c r="Q29">
+        <v>0.2048667762657865</v>
+      </c>
+      <c r="R29">
+        <v>0.3876189109431575</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
       <c r="A30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E30">
         <v>2017249867</v>
@@ -2299,16 +2479,22 @@
       <c r="P30">
         <v>0.01213083800785111</v>
       </c>
-    </row>
-    <row r="31" spans="1:16">
+      <c r="Q30">
+        <v>0.1799993325739057</v>
+      </c>
+      <c r="R30">
+        <v>0.3908858818454848</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
       <c r="A31" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E31">
         <v>2016918425</v>
@@ -2337,25 +2523,31 @@
       <c r="P31">
         <v>0.01282342907042703</v>
       </c>
-    </row>
-    <row r="32" spans="1:16">
+      <c r="Q31">
+        <v>0.2251363584204071</v>
+      </c>
+      <c r="R31">
+        <v>0.3036008429725566</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
       <c r="A32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D32">
-        <v>33.08786773681641</v>
+        <v>33.0878791809082</v>
       </c>
       <c r="E32">
         <v>632766400</v>
       </c>
       <c r="F32">
-        <v>20936890951.50146</v>
+        <v>20936898192.93823</v>
       </c>
       <c r="G32">
         <v>535803</v>
@@ -2367,13 +2559,13 @@
         <v>10805283</v>
       </c>
       <c r="J32">
-        <v>20944618643.50146</v>
+        <v>20944625884.93823</v>
       </c>
       <c r="K32">
         <v>0.02891079278960879</v>
       </c>
       <c r="L32">
-        <v>2.558189333116575E-05</v>
+        <v>2.558188448643088E-05</v>
       </c>
       <c r="M32">
         <v>0.03139723411223935</v>
@@ -2387,25 +2579,31 @@
       <c r="P32">
         <v>0.01587263341115972</v>
       </c>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="Q32">
+        <v>0.07945276338713059</v>
+      </c>
+      <c r="R32">
+        <v>0.4104690061493027</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18">
       <c r="A33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D33">
-        <v>40.38124847412109</v>
+        <v>40.38124465942383</v>
       </c>
       <c r="E33">
         <v>632510491</v>
       </c>
       <c r="F33">
-        <v>25541563299.55933</v>
+        <v>25541560886.72329</v>
       </c>
       <c r="G33">
         <v>734135</v>
@@ -2417,13 +2615,13 @@
         <v>11047953</v>
       </c>
       <c r="J33">
-        <v>25549318088.55933</v>
+        <v>25549315675.72329</v>
       </c>
       <c r="K33">
         <v>0.03904403942786643</v>
       </c>
       <c r="L33">
-        <v>2.873403499284533E-05</v>
+        <v>2.873403770644111E-05</v>
       </c>
       <c r="M33">
         <v>0.0456108022907049</v>
@@ -2437,25 +2635,31 @@
       <c r="P33">
         <v>0.02201517784045604</v>
       </c>
-    </row>
-    <row r="34" spans="1:16">
+      <c r="Q33">
+        <v>0.09747364970996801</v>
+      </c>
+      <c r="R33">
+        <v>0.429211429564044</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D34">
-        <v>33.08701324462891</v>
+        <v>33.08701705932617</v>
       </c>
       <c r="E34">
         <v>632654491</v>
       </c>
       <c r="F34">
-        <v>20932647522.99096</v>
+        <v>20932649936.37632</v>
       </c>
       <c r="G34">
         <v>735839</v>
@@ -2467,13 +2671,13 @@
         <v>11388432</v>
       </c>
       <c r="J34">
-        <v>20940513785.99096</v>
+        <v>20940516199.37632</v>
       </c>
       <c r="K34">
         <v>0.03821608184393468</v>
       </c>
       <c r="L34">
-        <v>3.51394912044742E-05</v>
+        <v>3.513948715466316E-05</v>
       </c>
       <c r="M34">
         <v>0.0438400123915215</v>
@@ -2487,25 +2691,31 @@
       <c r="P34">
         <v>0.021306028401466</v>
       </c>
-    </row>
-    <row r="35" spans="1:16">
+      <c r="Q34">
+        <v>0.09125764027293382</v>
+      </c>
+      <c r="R34">
+        <v>0.4196226580316915</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D35">
-        <v>16.78180313110352</v>
+        <v>16.78180694580078</v>
       </c>
       <c r="E35">
         <v>658883304</v>
       </c>
       <c r="F35">
-        <v>11057249894.09903</v>
+        <v>11057252407.53937</v>
       </c>
       <c r="G35">
         <v>1190339</v>
@@ -2517,13 +2727,13 @@
         <v>16920064</v>
       </c>
       <c r="J35">
-        <v>11064590811.09903</v>
+        <v>11064593324.53937</v>
       </c>
       <c r="K35">
         <v>0.04906392696981214</v>
       </c>
       <c r="L35">
-        <v>0.0001075809327540569</v>
+        <v>0.000107580908315901</v>
       </c>
       <c r="M35">
         <v>0.04463357821814386</v>
@@ -2537,25 +2747,31 @@
       <c r="P35">
         <v>0.02299110465151856</v>
       </c>
-    </row>
-    <row r="36" spans="1:16">
+      <c r="Q35">
+        <v>0.04782145992508376</v>
+      </c>
+      <c r="R35">
+        <v>0.2640520010934126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D36">
-        <v>19.63943672180176</v>
+        <v>19.63943481445312</v>
       </c>
       <c r="E36">
         <v>658883304</v>
       </c>
       <c r="F36">
-        <v>12940096955.95967</v>
+        <v>12940095699.2395</v>
       </c>
       <c r="G36">
         <v>1041530</v>
@@ -2567,13 +2783,13 @@
         <v>17506586</v>
       </c>
       <c r="J36">
-        <v>12948189248.95967</v>
+        <v>12948187992.2395</v>
       </c>
       <c r="K36">
         <v>0.04068654725076047</v>
       </c>
       <c r="L36">
-        <v>8.043827441614528E-05</v>
+        <v>8.043828222329187E-05</v>
       </c>
       <c r="M36">
         <v>0.03502259092663755</v>
@@ -2587,16 +2803,22 @@
       <c r="P36">
         <v>0.01851551208575903</v>
       </c>
-    </row>
-    <row r="37" spans="1:16">
+      <c r="Q36">
+        <v>0.04451872279488726</v>
+      </c>
+      <c r="R36">
+        <v>0.263225663446898</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C37" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D37">
         <v>18.12156105041504</v>
@@ -2637,16 +2859,22 @@
       <c r="P37">
         <v>0.01429786925190401</v>
       </c>
-    </row>
-    <row r="38" spans="1:16">
+      <c r="Q37">
+        <v>0.04359835380451408</v>
+      </c>
+      <c r="R37">
+        <v>0.2635131172931635</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D38">
         <v>24.55197525024414</v>
@@ -2687,16 +2915,22 @@
       <c r="P38">
         <v>0.01252022616335368</v>
       </c>
-    </row>
-    <row r="39" spans="1:16">
+      <c r="Q38">
+        <v>0.442592228151775</v>
+      </c>
+      <c r="R38">
+        <v>0.198844784623571</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D39">
         <v>29.69102096557617</v>
@@ -2737,25 +2971,31 @@
       <c r="P39">
         <v>0.02865578169972945</v>
       </c>
-    </row>
-    <row r="40" spans="1:16">
+      <c r="Q39">
+        <v>0.3931641187312033</v>
+      </c>
+      <c r="R39">
+        <v>0.1945654298256161</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D40">
-        <v>29.6079044342041</v>
+        <v>29.60790634155273</v>
       </c>
       <c r="E40">
         <v>1117020290</v>
       </c>
       <c r="F40">
-        <v>33072629997.38695</v>
+        <v>33072632127.93407</v>
       </c>
       <c r="G40">
         <v>2201374</v>
@@ -2767,13 +3007,13 @@
         <v>19573928</v>
       </c>
       <c r="J40">
-        <v>33075495602.38695</v>
+        <v>33075497732.93407</v>
       </c>
       <c r="K40">
         <v>0.09810248724873195</v>
       </c>
       <c r="L40">
-        <v>6.655603974808269E-05</v>
+        <v>6.655603546089765E-05</v>
       </c>
       <c r="M40">
         <v>0.04739391092069001</v>
@@ -2787,16 +3027,22 @@
       <c r="P40">
         <v>0.03794333725165874</v>
       </c>
-    </row>
-    <row r="41" spans="1:16">
+      <c r="Q40">
+        <v>0.4237974872000007</v>
+      </c>
+      <c r="R40">
+        <v>0.1870075200763051</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C41" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D41">
         <v>17.80377769470215</v>
@@ -2829,7 +3075,7 @@
         <v>0.1033345985480787</v>
       </c>
       <c r="N41" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -2837,25 +3083,31 @@
       <c r="P41">
         <v>0.09582091518006364</v>
       </c>
-    </row>
-    <row r="42" spans="1:16">
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18">
       <c r="A42" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C42" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D42">
-        <v>15.52421188354492</v>
+        <v>15.52421283721924</v>
       </c>
       <c r="E42">
         <v>393097</v>
       </c>
       <c r="F42">
-        <v>6102521.118785858</v>
+        <v>6102521.493672371</v>
       </c>
       <c r="G42">
         <v>158430</v>
@@ -2867,19 +3119,19 @@
         <v>7585763</v>
       </c>
       <c r="J42">
-        <v>5843175.118785858</v>
+        <v>5843175.493672371</v>
       </c>
       <c r="K42">
         <v>0.02162448574794473</v>
       </c>
       <c r="L42">
-        <v>0.02711368336208959</v>
+        <v>0.02711368162252962</v>
       </c>
       <c r="M42">
         <v>0.02305133972680138</v>
       </c>
       <c r="N42" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O42">
         <v>0</v>
@@ -2887,25 +3139,31 @@
       <c r="P42">
         <v>0.0228828921257893</v>
       </c>
-    </row>
-    <row r="43" spans="1:16">
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18">
       <c r="A43" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D43">
-        <v>15.88068866729736</v>
+        <v>15.880690574646</v>
       </c>
       <c r="E43">
         <v>393097</v>
       </c>
       <c r="F43">
-        <v>6242651.073048592</v>
+        <v>6242651.822821617</v>
       </c>
       <c r="G43">
         <v>485048</v>
@@ -2917,19 +3175,19 @@
         <v>8023719</v>
       </c>
       <c r="J43">
-        <v>5739587.073048592</v>
+        <v>5739587.822821617</v>
       </c>
       <c r="K43">
         <v>0.06449544620781035</v>
       </c>
       <c r="L43">
-        <v>0.08450921535412231</v>
+        <v>0.08450920431452644</v>
       </c>
       <c r="M43">
         <v>0.05351969579193887</v>
       </c>
       <c r="N43" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="O43">
         <v>0</v>
@@ -2937,16 +3195,22 @@
       <c r="P43">
         <v>0.05281561216935896</v>
       </c>
-    </row>
-    <row r="44" spans="1:16">
+      <c r="Q43">
+        <v>0</v>
+      </c>
+      <c r="R43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18">
       <c r="A44" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C44" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D44">
         <v>5.657915592193604</v>
@@ -2987,16 +3251,22 @@
       <c r="P44">
         <v>-0.03480374755473935</v>
       </c>
-    </row>
-    <row r="45" spans="1:16">
+      <c r="Q44">
+        <v>0.7047721430296723</v>
+      </c>
+      <c r="R44">
+        <v>0.3464268014326296</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C45" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D45">
         <v>6.194735527038574</v>
@@ -3037,16 +3307,22 @@
       <c r="P45">
         <v>-0.04072582709678355</v>
       </c>
-    </row>
-    <row r="46" spans="1:16">
+      <c r="Q45">
+        <v>0.7272666025469696</v>
+      </c>
+      <c r="R45">
+        <v>0.3577493024528077</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18">
       <c r="A46" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C46" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D46">
         <v>6.110085964202881</v>
@@ -3087,16 +3363,22 @@
       <c r="P46">
         <v>-0.007536336524909507</v>
       </c>
-    </row>
-    <row r="47" spans="1:16">
+      <c r="Q46">
+        <v>0.6885813272401409</v>
+      </c>
+      <c r="R46">
+        <v>0.2286712346425223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18">
       <c r="A47" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D47">
         <v>10.47000026702881</v>
@@ -3137,16 +3419,22 @@
       <c r="P47">
         <v>0.00875859843701649</v>
       </c>
-    </row>
-    <row r="48" spans="1:16">
+      <c r="Q47">
+        <v>0.09673222713684167</v>
+      </c>
+      <c r="R47">
+        <v>0.4264615892457747</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18">
       <c r="A48" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C48" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D48">
         <v>12.27000045776367</v>
@@ -3187,16 +3475,22 @@
       <c r="P48">
         <v>0.01532072071604826</v>
       </c>
-    </row>
-    <row r="49" spans="1:16">
+      <c r="Q48">
+        <v>0.09914470232275938</v>
+      </c>
+      <c r="R48">
+        <v>0.4137679422068002</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18">
       <c r="A49" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C49" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D49">
         <v>12.0600004196167</v>
@@ -3237,16 +3531,22 @@
       <c r="P49">
         <v>-0.002675781321551689</v>
       </c>
-    </row>
-    <row r="50" spans="1:16">
+      <c r="Q49">
+        <v>0.09179775538704987</v>
+      </c>
+      <c r="R49">
+        <v>0.4281252813864332</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18">
       <c r="A50" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C50" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D50">
         <v>39.29999923706055</v>
@@ -3287,16 +3587,22 @@
       <c r="P50">
         <v>-0.004250971035741808</v>
       </c>
-    </row>
-    <row r="51" spans="1:16">
+      <c r="Q50">
+        <v>0.01995871501860083</v>
+      </c>
+      <c r="R50">
+        <v>0.1244985040963989</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B51" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C51" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D51">
         <v>65.69999694824219</v>
@@ -3337,16 +3643,22 @@
       <c r="P51">
         <v>-0.004915268209918485</v>
       </c>
-    </row>
-    <row r="52" spans="1:16">
+      <c r="Q51">
+        <v>0.1165078817186108</v>
+      </c>
+      <c r="R51">
+        <v>0.1491323602846986</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
       <c r="A52" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C52" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D52">
         <v>70.5</v>
@@ -3387,25 +3699,31 @@
       <c r="P52">
         <v>-0.001694841558490607</v>
       </c>
-    </row>
-    <row r="53" spans="1:16">
+      <c r="Q52">
+        <v>0.02093085913289407</v>
+      </c>
+      <c r="R52">
+        <v>0.1424749347227344</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B53" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C53" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D53">
-        <v>13.9479923248291</v>
+        <v>13.94799327850342</v>
       </c>
       <c r="E53">
         <v>563649829</v>
       </c>
       <c r="F53">
-        <v>7861783488.783236</v>
+        <v>7861784026.321601</v>
       </c>
       <c r="G53">
         <v>4693643</v>
@@ -3417,13 +3735,13 @@
         <v>14770677</v>
       </c>
       <c r="J53">
-        <v>7861779519.783236</v>
+        <v>7861780057.321601</v>
       </c>
       <c r="K53">
         <v>0.3178530380637309</v>
       </c>
       <c r="L53">
-        <v>0.0005970204313398772</v>
+        <v>0.0005970203905194288</v>
       </c>
       <c r="M53">
         <v>0.2030475651183761</v>
@@ -3437,25 +3755,31 @@
       <c r="P53">
         <v>0.1525679063643121</v>
       </c>
-    </row>
-    <row r="54" spans="1:16">
+      <c r="Q53">
+        <v>0.03161151672892863</v>
+      </c>
+      <c r="R53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C54" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D54">
-        <v>20.09462928771973</v>
+        <v>20.09463119506836</v>
       </c>
       <c r="E54">
         <v>564327907</v>
       </c>
       <c r="F54">
-        <v>11339960087.87977</v>
+        <v>11339961164.24984</v>
       </c>
       <c r="G54">
         <v>318842</v>
@@ -3467,13 +3791,13 @@
         <v>14673459</v>
       </c>
       <c r="J54">
-        <v>11339958039.87977</v>
+        <v>11339959116.24984</v>
       </c>
       <c r="K54">
         <v>0.0217321974007817</v>
       </c>
       <c r="L54">
-        <v>2.811668252022742E-05</v>
+        <v>2.811667985143867E-05</v>
       </c>
       <c r="M54">
         <v>0.0122239752739964</v>
@@ -3487,16 +3811,22 @@
       <c r="P54">
         <v>0.009241162141776681</v>
       </c>
-    </row>
-    <row r="55" spans="1:16">
+      <c r="Q54">
+        <v>0.03349777018477378</v>
+      </c>
+      <c r="R54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C55" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D55">
         <v>18.41532707214355</v>
@@ -3537,25 +3867,31 @@
       <c r="P55">
         <v>0.002704812876346383</v>
       </c>
-    </row>
-    <row r="56" spans="1:16">
+      <c r="Q55">
+        <v>0.03420096205573739</v>
+      </c>
+      <c r="R55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18">
       <c r="A56" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B56" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C56" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D56">
-        <v>18.39130401611328</v>
+        <v>18.39130210876465</v>
       </c>
       <c r="E56">
         <v>2254639183</v>
       </c>
       <c r="F56">
-        <v>41465754661.19427</v>
+        <v>41465750360.8113</v>
       </c>
       <c r="G56">
         <v>1123605</v>
@@ -3567,13 +3903,13 @@
         <v>21911898</v>
       </c>
       <c r="J56">
-        <v>41495087296.19427</v>
+        <v>41495082995.8113</v>
       </c>
       <c r="K56">
         <v>0.02192633895209856</v>
       </c>
       <c r="L56">
-        <v>2.707802473048542E-05</v>
+        <v>2.707802753674265E-05</v>
       </c>
       <c r="M56">
         <v>0.01437880917481452</v>
@@ -3587,25 +3923,31 @@
       <c r="P56">
         <v>0.005303039522083313</v>
       </c>
-    </row>
-    <row r="57" spans="1:16">
+      <c r="Q56">
+        <v>0.1893535220709584</v>
+      </c>
+      <c r="R56">
+        <v>0.4955464193235599</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18">
       <c r="A57" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B57" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C57" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D57">
-        <v>28.50478744506836</v>
+        <v>28.50478553771973</v>
       </c>
       <c r="E57">
         <v>2254639183</v>
       </c>
       <c r="F57">
-        <v>64268010676.73758</v>
+        <v>64268006376.35462</v>
       </c>
       <c r="G57">
         <v>1394258</v>
@@ -3617,13 +3959,13 @@
         <v>21830544</v>
       </c>
       <c r="J57">
-        <v>64296934971.73758</v>
+        <v>64296930671.35462</v>
       </c>
       <c r="K57">
         <v>0.0274704447392691</v>
       </c>
       <c r="L57">
-        <v>2.168467284813594E-05</v>
+        <v>2.168467429847574E-05</v>
       </c>
       <c r="M57">
         <v>0.01457650345314345</v>
@@ -3637,25 +3979,31 @@
       <c r="P57">
         <v>0.005446224283708282</v>
       </c>
-    </row>
-    <row r="58" spans="1:16">
+      <c r="Q57">
+        <v>0.1982099906064171</v>
+      </c>
+      <c r="R57">
+        <v>0.4953678434474731</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18">
       <c r="A58" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C58" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D58">
-        <v>22.00202369689941</v>
+        <v>22.00202178955078</v>
       </c>
       <c r="E58">
         <v>2254606710</v>
       </c>
       <c r="F58">
-        <v>49605910260.60843</v>
+        <v>49605905960.2874</v>
       </c>
       <c r="G58">
         <v>1489544</v>
@@ -3667,13 +4015,13 @@
         <v>22125810</v>
       </c>
       <c r="J58">
-        <v>49636165122.60843</v>
+        <v>49636160822.2874</v>
       </c>
       <c r="K58">
         <v>0.02843690130588626</v>
       </c>
       <c r="L58">
-        <v>3.000924822295625E-05</v>
+        <v>3.000925082286324E-05</v>
       </c>
       <c r="M58">
         <v>0.03113775269696341</v>
@@ -3687,25 +4035,31 @@
       <c r="P58">
         <v>0.0113788850553044</v>
       </c>
-    </row>
-    <row r="59" spans="1:16">
+      <c r="Q58">
+        <v>0.1954720907403932</v>
+      </c>
+      <c r="R58">
+        <v>0.5038830692170198</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18">
       <c r="A59" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B59" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C59" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D59">
-        <v>12.1156005859375</v>
+        <v>12.11560153961182</v>
       </c>
       <c r="E59">
         <v>15745974</v>
       </c>
       <c r="F59">
-        <v>190771931.8205566</v>
+        <v>190771946.8370876</v>
       </c>
       <c r="G59">
         <v>4875526</v>
@@ -3717,13 +4071,13 @@
         <v>84999591</v>
       </c>
       <c r="J59">
-        <v>189633596.8205566</v>
+        <v>189633611.8370876</v>
       </c>
       <c r="K59">
         <v>0.05813800356150163</v>
       </c>
       <c r="L59">
-        <v>0.02571024376346947</v>
+        <v>0.02571024172755047</v>
       </c>
       <c r="M59">
         <v>0.04493255738136434</v>
@@ -3737,25 +4091,31 @@
       <c r="P59">
         <v>0.02898643856299874</v>
       </c>
-    </row>
-    <row r="60" spans="1:16">
+      <c r="Q59">
+        <v>0.155826998203254</v>
+      </c>
+      <c r="R59">
+        <v>0.01543868554745016</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B60" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C60" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D60">
-        <v>13.02870845794678</v>
+        <v>13.02871036529541</v>
       </c>
       <c r="E60">
         <v>15746689</v>
       </c>
       <c r="F60">
-        <v>205159020.1589575</v>
+        <v>205159050.1933832</v>
       </c>
       <c r="G60">
         <v>3445417</v>
@@ -3767,13 +4127,13 @@
         <v>85074603</v>
       </c>
       <c r="J60">
-        <v>204411899.1589575</v>
+        <v>204411929.1933832</v>
       </c>
       <c r="K60">
         <v>0.04085758187348699</v>
       </c>
       <c r="L60">
-        <v>0.01685526632341853</v>
+        <v>0.01685526384685932</v>
       </c>
       <c r="M60">
         <v>0.03053508225010465</v>
@@ -3787,25 +4147,31 @@
       <c r="P60">
         <v>0.01984246544710798</v>
       </c>
-    </row>
-    <row r="61" spans="1:16">
+      <c r="Q60">
+        <v>0.1443494295317918</v>
+      </c>
+      <c r="R60">
+        <v>0.01740273954438239</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18">
       <c r="A61" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B61" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C61" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D61">
-        <v>11.08412647247314</v>
+        <v>11.08412551879883</v>
       </c>
       <c r="E61">
         <v>15742975</v>
       </c>
       <c r="F61">
-        <v>174497125.9529829</v>
+        <v>174497110.939312</v>
       </c>
       <c r="G61">
         <v>4897578</v>
@@ -3817,13 +4183,13 @@
         <v>90254900</v>
       </c>
       <c r="J61">
-        <v>170819967.9529829</v>
+        <v>170819952.939312</v>
       </c>
       <c r="K61">
         <v>0.05656855777088758</v>
       </c>
       <c r="L61">
-        <v>0.0286709923827408</v>
+        <v>0.02867099490268555</v>
       </c>
       <c r="M61">
         <v>0.04448516368640373</v>
@@ -3837,16 +4203,22 @@
       <c r="P61">
         <v>0.029425302142036</v>
       </c>
-    </row>
-    <row r="62" spans="1:16">
+      <c r="Q61">
+        <v>0.1489055487804954</v>
+      </c>
+      <c r="R61">
+        <v>0.01522965641255883</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18">
       <c r="A62" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B62" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C62" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D62">
         <v>12.13980484008789</v>
@@ -3887,25 +4259,31 @@
       <c r="P62">
         <v>0.01054505456625748</v>
       </c>
-    </row>
-    <row r="63" spans="1:16">
+      <c r="Q62">
+        <v>0.1233532577576995</v>
+      </c>
+      <c r="R62">
+        <v>0.2463667090681464</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18">
       <c r="A63" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B63" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C63" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D63">
-        <v>19.56565093994141</v>
+        <v>19.56565475463867</v>
       </c>
       <c r="E63">
         <v>586242289</v>
       </c>
       <c r="F63">
-        <v>11470211992.80625</v>
+        <v>11470214229.14311</v>
       </c>
       <c r="G63">
         <v>404558</v>
@@ -3917,13 +4295,13 @@
         <v>4567617</v>
       </c>
       <c r="J63">
-        <v>11471986033.80625</v>
+        <v>11471988270.14311</v>
       </c>
       <c r="K63">
         <v>0.0637937271294037</v>
       </c>
       <c r="L63">
-        <v>3.526486162098064E-05</v>
+        <v>3.526485474648706E-05</v>
       </c>
       <c r="M63">
         <v>0.05737346191679382</v>
@@ -3937,25 +4315,31 @@
       <c r="P63">
         <v>0.03212310875595582</v>
       </c>
-    </row>
-    <row r="64" spans="1:16">
+      <c r="Q63">
+        <v>0.1277808626879905</v>
+      </c>
+      <c r="R63">
+        <v>0.2331434581312309</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18">
       <c r="A64" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B64" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D64">
-        <v>19.56565475463867</v>
+        <v>19.56565093994141</v>
       </c>
       <c r="E64">
         <v>586242289</v>
       </c>
       <c r="F64">
-        <v>11470214229.14311</v>
+        <v>11470211992.80625</v>
       </c>
       <c r="G64">
         <v>213229</v>
@@ -3967,13 +4351,13 @@
         <v>4713060</v>
       </c>
       <c r="J64">
-        <v>11472085509.14311</v>
+        <v>11472083272.80625</v>
       </c>
       <c r="K64">
         <v>0.03238426326708523</v>
       </c>
       <c r="L64">
-        <v>1.858676871176206E-05</v>
+        <v>1.858677233501643E-05</v>
       </c>
       <c r="M64">
         <v>0.01306412394495296</v>
@@ -3987,16 +4371,22 @@
       <c r="P64">
         <v>0.007331068241372314</v>
       </c>
-    </row>
-    <row r="65" spans="1:16">
+      <c r="Q64">
+        <v>0.1296843730562644</v>
+      </c>
+      <c r="R64">
+        <v>0.2280618032913367</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B65" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C65" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E65">
         <v>734633</v>
@@ -4025,16 +4415,22 @@
       <c r="P65">
         <v>-0.008057569155158465</v>
       </c>
-    </row>
-    <row r="66" spans="1:16">
+      <c r="Q65">
+        <v>0.07934927398610092</v>
+      </c>
+      <c r="R65">
+        <v>0.3910952318382591</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B66" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E66">
         <v>734633</v>
@@ -4063,16 +4459,22 @@
       <c r="P66">
         <v>-0.002842730222490773</v>
       </c>
-    </row>
-    <row r="67" spans="1:16">
+      <c r="Q66">
+        <v>0.1365471731481272</v>
+      </c>
+      <c r="R66">
+        <v>0.3929784093305224</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B67" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C67" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E67">
         <v>734633</v>
@@ -4101,25 +4503,31 @@
       <c r="P67">
         <v>0.006782532924506445</v>
       </c>
-    </row>
-    <row r="68" spans="1:16">
+      <c r="Q67">
+        <v>0.1328230999821566</v>
+      </c>
+      <c r="R67">
+        <v>0.3578779180781429</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18">
       <c r="A68" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B68" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C68" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D68">
-        <v>21.67304611206055</v>
+        <v>21.67304801940918</v>
       </c>
       <c r="E68">
         <v>585281980</v>
       </c>
       <c r="F68">
-        <v>12684843341.0981</v>
+        <v>12684844457.43488</v>
       </c>
       <c r="G68">
         <v>310789</v>
@@ -4131,13 +4539,13 @@
         <v>6723245</v>
       </c>
       <c r="J68">
-        <v>12687023030.0981</v>
+        <v>12687024146.43488</v>
       </c>
       <c r="K68">
         <v>0.03490860428708109</v>
       </c>
       <c r="L68">
-        <v>2.44966056467856E-05</v>
+        <v>2.449660349131859E-05</v>
       </c>
       <c r="M68">
         <v>0.03082410353928795</v>
@@ -4151,25 +4559,31 @@
       <c r="P68">
         <v>0.01962582535043952</v>
       </c>
-    </row>
-    <row r="69" spans="1:16">
+      <c r="Q68">
+        <v>0.04401591218636873</v>
+      </c>
+      <c r="R68">
+        <v>0.269010689378447</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18">
       <c r="A69" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B69" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C69" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D69">
-        <v>24.55806159973145</v>
+        <v>24.55805778503418</v>
       </c>
       <c r="E69">
         <v>584281980</v>
       </c>
       <c r="F69">
-        <v>14348832856.45306</v>
+        <v>14348830627.59418</v>
       </c>
       <c r="G69">
         <v>333333</v>
@@ -4181,13 +4595,13 @@
         <v>6812013</v>
       </c>
       <c r="J69">
-        <v>14350963481.45306</v>
+        <v>14350961252.59418</v>
       </c>
       <c r="K69">
         <v>0.03727457155260003</v>
       </c>
       <c r="L69">
-        <v>2.322722097584556E-05</v>
+        <v>2.322722458328318E-05</v>
       </c>
       <c r="M69">
         <v>0.03629984264563206</v>
@@ -4201,16 +4615,22 @@
       <c r="P69">
         <v>0.02395732239536601</v>
       </c>
-    </row>
-    <row r="70" spans="1:16">
+      <c r="Q69">
+        <v>0.04724361692738027</v>
+      </c>
+      <c r="R69">
+        <v>0.2404925689428812</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
       <c r="A70" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B70" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C70" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D70">
         <v>21.99642562866211</v>
@@ -4251,25 +4671,31 @@
       <c r="P70">
         <v>0.02511511543483577</v>
       </c>
-    </row>
-    <row r="71" spans="1:16">
+      <c r="Q70">
+        <v>0.04830152592606012</v>
+      </c>
+      <c r="R70">
+        <v>0.2381346603886108</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
       <c r="A71" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C71" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D71">
-        <v>26.73405456542969</v>
+        <v>26.73405075073242</v>
       </c>
       <c r="E71">
         <v>1033497</v>
       </c>
       <c r="F71">
-        <v>27629565.19120789</v>
+        <v>27629561.24872971</v>
       </c>
       <c r="G71">
         <v>729623</v>
@@ -4281,13 +4707,13 @@
         <v>6491155</v>
       </c>
       <c r="J71">
-        <v>35110665.19120789</v>
+        <v>35110661.24872971</v>
       </c>
       <c r="K71">
         <v>0.05221941626459008</v>
       </c>
       <c r="L71">
-        <v>0.02078066581839372</v>
+        <v>0.0207806681517967</v>
       </c>
       <c r="M71">
         <v>0.05958446532242721</v>
@@ -4301,25 +4727,31 @@
       <c r="P71">
         <v>0.02402731260833807</v>
       </c>
-    </row>
-    <row r="72" spans="1:16">
+      <c r="Q71">
+        <v>0.04304573577199635</v>
+      </c>
+      <c r="R71">
+        <v>0.5135452598812177</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
       <c r="A72" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C72" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D72">
-        <v>28.95154571533203</v>
+        <v>28.95154762268066</v>
       </c>
       <c r="E72">
         <v>1033497</v>
       </c>
       <c r="F72">
-        <v>29921335.64215851</v>
+        <v>29921337.6133976</v>
       </c>
       <c r="G72">
         <v>470720</v>
@@ -4331,13 +4763,13 @@
         <v>6689301</v>
       </c>
       <c r="J72">
-        <v>37305922.64215851</v>
+        <v>37305924.6133976</v>
       </c>
       <c r="K72">
         <v>0.03344633693262303</v>
       </c>
       <c r="L72">
-        <v>0.01261783563203047</v>
+        <v>0.01261783496530606</v>
       </c>
       <c r="M72">
         <v>0.03293707369424698</v>
@@ -4351,16 +4783,22 @@
       <c r="P72">
         <v>0.01345078107887076</v>
       </c>
-    </row>
-    <row r="73" spans="1:16">
+      <c r="Q72">
+        <v>0.04142229589398495</v>
+      </c>
+      <c r="R72">
+        <v>0.5082189653290407</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
       <c r="A73" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C73" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D73">
         <v>27.26494979858398</v>
@@ -4401,16 +4839,22 @@
       <c r="P73">
         <v>0.01652563341734722</v>
       </c>
-    </row>
-    <row r="74" spans="1:16">
+      <c r="Q73">
+        <v>0.04066897587840008</v>
+      </c>
+      <c r="R73">
+        <v>0.5314002260631673</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
       <c r="A74" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B74" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C74" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D74">
         <v>6.380000114440918</v>
@@ -4451,16 +4895,22 @@
       <c r="P74">
         <v>0.002783306066918505</v>
       </c>
-    </row>
-    <row r="75" spans="1:16">
+      <c r="Q74">
+        <v>0.1154621752969015</v>
+      </c>
+      <c r="R74">
+        <v>0.3012110278390733</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
       <c r="A75" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B75" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C75" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D75">
         <v>11.56999969482422</v>
@@ -4501,16 +4951,22 @@
       <c r="P75">
         <v>0.01294121348887532</v>
       </c>
-    </row>
-    <row r="76" spans="1:16">
+      <c r="Q75">
+        <v>0.1227464148777698</v>
+      </c>
+      <c r="R75">
+        <v>0.3143148324002589</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
       <c r="A76" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B76" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C76" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D76">
         <v>10.67000007629395</v>
@@ -4551,16 +5007,22 @@
       <c r="P76">
         <v>-0.009197067233145013</v>
       </c>
-    </row>
-    <row r="77" spans="1:16">
+      <c r="Q76">
+        <v>0.1299083360611329</v>
+      </c>
+      <c r="R76">
+        <v>0.2686297959439173</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
       <c r="A77" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B77" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C77" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D77">
         <v>6.275968551635742</v>
@@ -4601,16 +5063,22 @@
       <c r="P77">
         <v>0.02171557234166182</v>
       </c>
-    </row>
-    <row r="78" spans="1:16">
+      <c r="Q77">
+        <v>0.1907799244625218</v>
+      </c>
+      <c r="R77">
+        <v>0.545601975595584</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
       <c r="A78" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B78" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C78" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D78">
         <v>17.64392852783203</v>
@@ -4651,16 +5119,22 @@
       <c r="P78">
         <v>0.004605612210584645</v>
       </c>
-    </row>
-    <row r="79" spans="1:16">
+      <c r="Q78">
+        <v>0.1879608270759241</v>
+      </c>
+      <c r="R78">
+        <v>0.5454124659202804</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18">
       <c r="A79" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B79" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C79" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D79">
         <v>17.90774154663086</v>
@@ -4701,25 +5175,31 @@
       <c r="P79">
         <v>0.01341984006287217</v>
       </c>
-    </row>
-    <row r="80" spans="1:16">
+      <c r="Q79">
+        <v>0.18635525508835</v>
+      </c>
+      <c r="R79">
+        <v>0.5310095752721948</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18">
       <c r="A80" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B80" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C80" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D80">
-        <v>3.308878660202026</v>
+        <v>3.308878183364868</v>
       </c>
       <c r="E80">
         <v>5485338838</v>
       </c>
       <c r="F80">
-        <v>18150320625.03558</v>
+        <v>18150318009.4222</v>
       </c>
       <c r="G80">
         <v>1148539</v>
@@ -4731,13 +5211,13 @@
         <v>12089845</v>
       </c>
       <c r="J80">
-        <v>18149675328.03558</v>
+        <v>18149672712.4222</v>
       </c>
       <c r="K80">
         <v>0.1003568686155189</v>
       </c>
       <c r="L80">
-        <v>6.328151767133079E-05</v>
+        <v>6.328152679105362E-05</v>
       </c>
       <c r="M80">
         <v>0.04266373969227893</v>
@@ -4751,16 +5231,22 @@
       <c r="P80">
         <v>0.01848391993070259</v>
       </c>
-    </row>
-    <row r="81" spans="1:16">
+      <c r="Q80">
+        <v>0.1617736647770805</v>
+      </c>
+      <c r="R80">
+        <v>0.2972230866560202</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18">
       <c r="A81" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B81" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C81" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D81">
         <v>3.150222063064575</v>
@@ -4801,16 +5287,22 @@
       <c r="P81">
         <v>0.01892045068852682</v>
       </c>
-    </row>
-    <row r="82" spans="1:16">
+      <c r="Q81">
+        <v>0.1536823878480858</v>
+      </c>
+      <c r="R81">
+        <v>0.2901291215347243</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18">
       <c r="A82" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B82" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C82" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D82">
         <v>3.65516209602356</v>
@@ -4851,25 +5343,31 @@
       <c r="P82">
         <v>0.04075690373668411</v>
       </c>
-    </row>
-    <row r="83" spans="1:16">
+      <c r="Q82">
+        <v>0.1643810993283561</v>
+      </c>
+      <c r="R82">
+        <v>0.2869503732696481</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18">
       <c r="A83" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C83" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D83">
-        <v>9.323643684387207</v>
+        <v>9.32364559173584</v>
       </c>
       <c r="E83">
         <v>5752295687</v>
       </c>
       <c r="F83">
-        <v>53632355352.82532</v>
+        <v>53632366324.45863</v>
       </c>
       <c r="G83">
         <v>1356975</v>
@@ -4881,13 +5379,13 @@
         <v>20547544</v>
       </c>
       <c r="J83">
-        <v>53643933019.82532</v>
+        <v>53643943991.45863</v>
       </c>
       <c r="K83">
         <v>0.04224018948856087</v>
       </c>
       <c r="L83">
-        <v>2.529596402818748E-05</v>
+        <v>2.529595885448061E-05</v>
       </c>
       <c r="M83">
         <v>0.05302132459236977</v>
@@ -4901,16 +5399,22 @@
       <c r="P83">
         <v>0.02352253362070723</v>
       </c>
-    </row>
-    <row r="84" spans="1:16">
+      <c r="Q83">
+        <v>0.0531243274390364</v>
+      </c>
+      <c r="R83">
+        <v>0.2874187658629387</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18">
       <c r="A84" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C84" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D84">
         <v>13.27007484436035</v>
@@ -4951,16 +5455,22 @@
       <c r="P84">
         <v>0.02203973931559553</v>
       </c>
-    </row>
-    <row r="85" spans="1:16">
+      <c r="Q84">
+        <v>0.05185007638875327</v>
+      </c>
+      <c r="R84">
+        <v>0.2720409795116884</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18">
       <c r="A85" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C85" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D85">
         <v>11.25736904144287</v>
@@ -5001,16 +5511,22 @@
       <c r="P85">
         <v>0.02266871422996</v>
       </c>
-    </row>
-    <row r="86" spans="1:16">
+      <c r="Q85">
+        <v>0.05254266915059407</v>
+      </c>
+      <c r="R85">
+        <v>0.2576625156652181</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18">
       <c r="A86" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C86" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D86">
         <v>31.13998413085938</v>
@@ -5051,16 +5567,22 @@
       <c r="P86">
         <v>0.1064002682382017</v>
       </c>
-    </row>
-    <row r="87" spans="1:16">
+      <c r="Q86">
+        <v>0.2577411479379096</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18">
       <c r="A87" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B87" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C87" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D87">
         <v>37.02053833007812</v>
@@ -5101,16 +5623,22 @@
       <c r="P87">
         <v>0.07400830278801578</v>
       </c>
-    </row>
-    <row r="88" spans="1:16">
+      <c r="Q87">
+        <v>0.2033944574098198</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18">
       <c r="A88" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B88" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C88" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D88">
         <v>46.96456909179688</v>
@@ -5151,16 +5679,22 @@
       <c r="P88">
         <v>0.1209306863108822</v>
       </c>
-    </row>
-    <row r="89" spans="1:16">
+      <c r="Q88">
+        <v>0.3003540481745178</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18">
       <c r="A89" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B89" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C89" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D89">
         <v>38.52667617797852</v>
@@ -5201,25 +5735,31 @@
       <c r="P89">
         <v>0.03885818911450875</v>
       </c>
-    </row>
-    <row r="90" spans="1:16">
+      <c r="Q89">
+        <v>0.08357755553988715</v>
+      </c>
+      <c r="R89">
+        <v>0.1004265697721737</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18">
       <c r="A90" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B90" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C90" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D90">
-        <v>40.95311737060547</v>
+        <v>40.95312118530273</v>
       </c>
       <c r="E90">
         <v>1291650715</v>
       </c>
       <c r="F90">
-        <v>52897123333.22147</v>
+        <v>52897128260.47792</v>
       </c>
       <c r="G90">
         <v>3068677</v>
@@ -5231,13 +5771,13 @@
         <v>42587449</v>
       </c>
       <c r="J90">
-        <v>52912482146.22147</v>
+        <v>52912487073.47792</v>
       </c>
       <c r="K90">
         <v>0.05295728998015437</v>
       </c>
       <c r="L90">
-        <v>5.799533258560498E-05</v>
+        <v>5.799532718502957E-05</v>
       </c>
       <c r="M90">
         <v>0.119228155694416</v>
@@ -5251,16 +5791,22 @@
       <c r="P90">
         <v>0.03772886151952198</v>
       </c>
-    </row>
-    <row r="91" spans="1:16">
+      <c r="Q90">
+        <v>0.06805990967732443</v>
+      </c>
+      <c r="R90">
+        <v>0.1328033711509413</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18">
       <c r="A91" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B91" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C91" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D91">
         <v>50.26990509033203</v>
@@ -5301,25 +5847,31 @@
       <c r="P91">
         <v>-0.005332226767581256</v>
       </c>
-    </row>
-    <row r="92" spans="1:16">
+      <c r="Q91">
+        <v>0.06547152814348961</v>
+      </c>
+      <c r="R91">
+        <v>0.1419921801002345</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18">
       <c r="A92" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B92" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C92" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D92">
-        <v>54.53847122192383</v>
+        <v>54.53847503662109</v>
       </c>
       <c r="E92">
         <v>110186077</v>
       </c>
       <c r="F92">
-        <v>6009380189.521183</v>
+        <v>6009380609.84771</v>
       </c>
       <c r="G92">
         <v>104824</v>
@@ -5331,13 +5883,13 @@
         <v>2716661</v>
       </c>
       <c r="J92">
-        <v>6010076763.521183</v>
+        <v>6010077183.84771</v>
       </c>
       <c r="K92">
         <v>0.03071104099190358</v>
       </c>
       <c r="L92">
-        <v>1.744137456550317E-05</v>
+        <v>1.744137334570646E-05</v>
       </c>
       <c r="M92">
         <v>0.02333195050836302</v>
@@ -5351,25 +5903,31 @@
       <c r="P92">
         <v>0.0135792574673062</v>
       </c>
-    </row>
-    <row r="93" spans="1:16">
+      <c r="Q92">
+        <v>0.2196527643434857</v>
+      </c>
+      <c r="R92">
+        <v>0.1503213197020169</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18">
       <c r="A93" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B93" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C93" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D93">
-        <v>67.90044403076172</v>
+        <v>67.90045166015625</v>
       </c>
       <c r="E93">
         <v>110848770</v>
       </c>
       <c r="F93">
-        <v>7526680703.263779</v>
+        <v>7526681548.972778</v>
       </c>
       <c r="G93">
         <v>125468</v>
@@ -5381,13 +5939,13 @@
         <v>2783100</v>
       </c>
       <c r="J93">
-        <v>7527353692.263779</v>
+        <v>7527354537.972778</v>
       </c>
       <c r="K93">
         <v>0.03630346324993367</v>
       </c>
       <c r="L93">
-        <v>1.666827481867226E-05</v>
+        <v>1.666827294596785E-05</v>
       </c>
       <c r="M93">
         <v>0.03609715784556789</v>
@@ -5401,16 +5959,22 @@
       <c r="P93">
         <v>0.02081415583040633</v>
       </c>
-    </row>
-    <row r="94" spans="1:16">
+      <c r="Q93">
+        <v>0.2343302837866424</v>
+      </c>
+      <c r="R93">
+        <v>0.1410498736278956</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18">
       <c r="A94" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B94" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C94" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D94">
         <v>56.38967132568359</v>
@@ -5451,16 +6015,22 @@
       <c r="P94">
         <v>0.0230414569041557</v>
       </c>
-    </row>
-    <row r="95" spans="1:16">
+      <c r="Q94">
+        <v>0.2566155141106573</v>
+      </c>
+      <c r="R94">
+        <v>0.1433458868167341</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18">
       <c r="A95" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B95" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C95" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D95">
         <v>3.96722412109375</v>
@@ -5501,25 +6071,31 @@
       <c r="P95">
         <v>0.02646632369524302</v>
       </c>
-    </row>
-    <row r="96" spans="1:16">
+      <c r="Q95">
+        <v>0.2040941221798157</v>
+      </c>
+      <c r="R95">
+        <v>0.4652725868363871</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18">
       <c r="A96" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B96" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C96" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D96">
-        <v>4.898534774780273</v>
+        <v>4.898534297943115</v>
       </c>
       <c r="E96">
         <v>172693506</v>
       </c>
       <c r="F96">
-        <v>845945144.5197258</v>
+        <v>845945062.1730452</v>
       </c>
       <c r="G96">
         <v>129488</v>
@@ -5531,13 +6107,13 @@
         <v>1456031</v>
       </c>
       <c r="J96">
-        <v>846919591.5197258</v>
+        <v>846919509.1730452</v>
       </c>
       <c r="K96">
         <v>0.0532767628425355</v>
       </c>
       <c r="L96">
-        <v>0.0001528929089568523</v>
+        <v>0.0001528929238227556</v>
       </c>
       <c r="M96">
         <v>0.07882524479217819</v>
@@ -5551,25 +6127,31 @@
       <c r="P96">
         <v>0.03911595461442299</v>
       </c>
-    </row>
-    <row r="97" spans="1:16">
+      <c r="Q96">
+        <v>0.2063317869446258</v>
+      </c>
+      <c r="R96">
+        <v>0.4462491326272567</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18">
       <c r="A97" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B97" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C97" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D97">
-        <v>4.781368255615234</v>
+        <v>4.781368732452393</v>
       </c>
       <c r="E97">
         <v>172693506</v>
       </c>
       <c r="F97">
-        <v>825711247.539299</v>
+        <v>825711329.8859797</v>
       </c>
       <c r="G97">
         <v>109150</v>
@@ -5581,13 +6163,13 @@
         <v>1934466</v>
       </c>
       <c r="J97">
-        <v>826353947.539299</v>
+        <v>826354029.8859797</v>
       </c>
       <c r="K97">
         <v>0.04235272388352167</v>
       </c>
       <c r="L97">
-        <v>0.0001320862571359703</v>
+        <v>0.0001320862439734947</v>
       </c>
       <c r="M97">
         <v>0.04439209580318289</v>
@@ -5601,16 +6183,22 @@
       <c r="P97">
         <v>0.02621052168934023</v>
       </c>
-    </row>
-    <row r="98" spans="1:16">
+      <c r="Q97">
+        <v>0.1702098306777408</v>
+      </c>
+      <c r="R97">
+        <v>0.3546949720970493</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18">
       <c r="A98" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B98" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C98" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E98">
         <v>982845</v>
@@ -5639,16 +6227,22 @@
       <c r="P98">
         <v>0.01176534946234133</v>
       </c>
-    </row>
-    <row r="99" spans="1:16">
+      <c r="Q98">
+        <v>0.1539766528819353</v>
+      </c>
+      <c r="R98">
+        <v>0.4011577911103371</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18">
       <c r="A99" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B99" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C99" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E99">
         <v>1055019</v>
@@ -5677,16 +6271,22 @@
       <c r="P99">
         <v>-0.001785556317525582</v>
       </c>
-    </row>
-    <row r="100" spans="1:16">
+      <c r="Q99">
+        <v>0.1377049087340981</v>
+      </c>
+      <c r="R99">
+        <v>0.3915201572897085</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18">
       <c r="A100" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B100" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C100" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E100">
         <v>1054820662</v>
@@ -5715,25 +6315,31 @@
       <c r="P100">
         <v>0.01279390341056036</v>
       </c>
-    </row>
-    <row r="101" spans="1:16">
+      <c r="Q100">
+        <v>0.1409371455136644</v>
+      </c>
+      <c r="R100">
+        <v>0.3849159834902771</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18">
       <c r="A101" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B101" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C101" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D101">
-        <v>5.862680912017822</v>
+        <v>5.86268138885498</v>
       </c>
       <c r="E101">
         <v>2200525</v>
       </c>
       <c r="F101">
-        <v>12900975.91391802</v>
+        <v>12900976.96321011</v>
       </c>
       <c r="G101">
         <v>1859305</v>
@@ -5745,13 +6351,13 @@
         <v>22791065</v>
       </c>
       <c r="J101">
-        <v>12732144.91391802</v>
+        <v>12732145.96321011</v>
       </c>
       <c r="K101">
         <v>0.08218927449870778</v>
       </c>
       <c r="L101">
-        <v>0.1460323466761299</v>
+        <v>0.146032334641192</v>
       </c>
       <c r="M101">
         <v>0.06134886632107802</v>
@@ -5765,25 +6371,31 @@
       <c r="P101">
         <v>0.05310928417105507</v>
       </c>
-    </row>
-    <row r="102" spans="1:16">
+      <c r="Q101">
+        <v>0.3284441880110731</v>
+      </c>
+      <c r="R101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18">
       <c r="A102" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B102" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C102" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D102">
-        <v>6.751915454864502</v>
+        <v>6.751913547515869</v>
       </c>
       <c r="E102">
         <v>2200525</v>
       </c>
       <c r="F102">
-        <v>14857758.75631571</v>
+        <v>14857754.55914736</v>
       </c>
       <c r="G102">
         <v>1575671</v>
@@ -5795,13 +6407,13 @@
         <v>23609050</v>
       </c>
       <c r="J102">
-        <v>14572240.75631571</v>
+        <v>14572236.55914736</v>
       </c>
       <c r="K102">
         <v>0.06755713499996484</v>
       </c>
       <c r="L102">
-        <v>0.1081282574416082</v>
+        <v>0.1081282885852489</v>
       </c>
       <c r="M102">
         <v>0.05275019536999583</v>
@@ -5815,16 +6427,22 @@
       <c r="P102">
         <v>0.04671491218264797</v>
       </c>
-    </row>
-    <row r="103" spans="1:16">
+      <c r="Q102">
+        <v>0.330824568002726</v>
+      </c>
+      <c r="R102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18">
       <c r="A103" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B103" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D103">
         <v>6.612715721130371</v>
@@ -5865,25 +6483,31 @@
       <c r="P103">
         <v>0.04417412210096691</v>
       </c>
-    </row>
-    <row r="104" spans="1:16">
+      <c r="Q103">
+        <v>0.3365478902540078</v>
+      </c>
+      <c r="R103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18">
       <c r="A104" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C104" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D104">
-        <v>11.59996509552002</v>
+        <v>11.59996604919434</v>
       </c>
       <c r="E104">
         <v>379181</v>
       </c>
       <c r="F104">
-        <v>4398486.364884377</v>
+        <v>4398486.726499557</v>
       </c>
       <c r="G104">
         <v>490723</v>
@@ -5895,13 +6519,13 @@
         <v>7460638</v>
       </c>
       <c r="J104">
-        <v>7417219.364884377</v>
+        <v>7417219.726499557</v>
       </c>
       <c r="K104">
         <v>0.04682752428557019</v>
       </c>
       <c r="L104">
-        <v>0.0661599685622416</v>
+        <v>0.06615996533671373</v>
       </c>
       <c r="M104">
         <v>0.04526502961274893</v>
@@ -5915,25 +6539,31 @@
       <c r="P104">
         <v>0.02493808972605142</v>
       </c>
-    </row>
-    <row r="105" spans="1:16">
+      <c r="Q104">
+        <v>0.1278735616268916</v>
+      </c>
+      <c r="R104">
+        <v>0.3000386581522733</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18">
       <c r="A105" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B105" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C105" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D105">
-        <v>15.8543701171875</v>
+        <v>15.85436820983887</v>
       </c>
       <c r="E105">
         <v>379181</v>
       </c>
       <c r="F105">
-        <v>6011675.915405273</v>
+        <v>6011675.192174911</v>
       </c>
       <c r="G105">
         <v>325300</v>
@@ -5945,13 +6575,13 @@
         <v>7581403</v>
       </c>
       <c r="J105">
-        <v>9260970.915405273</v>
+        <v>9260970.192174911</v>
       </c>
       <c r="K105">
         <v>0.0300349986676759</v>
       </c>
       <c r="L105">
-        <v>0.03512590666480507</v>
+        <v>0.03512590940794338</v>
       </c>
       <c r="M105">
         <v>0.032879930007678</v>
@@ -5965,25 +6595,31 @@
       <c r="P105">
         <v>0.01846648110992681</v>
       </c>
-    </row>
-    <row r="106" spans="1:16">
+      <c r="Q105">
+        <v>0.1333300145286601</v>
+      </c>
+      <c r="R105">
+        <v>0.2955705217842486</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18">
       <c r="A106" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B106" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C106" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D106">
-        <v>13.22022819519043</v>
+        <v>13.22023105621338</v>
       </c>
       <c r="E106">
         <v>379181</v>
       </c>
       <c r="F106">
-        <v>5012859.347280502</v>
+        <v>5012860.432126045</v>
       </c>
       <c r="G106">
         <v>492874</v>
@@ -5995,13 +6631,13 @@
         <v>7891106</v>
       </c>
       <c r="J106">
-        <v>8405881.347280502</v>
+        <v>8405882.432126045</v>
       </c>
       <c r="K106">
         <v>0.04367851906678123</v>
       </c>
       <c r="L106">
-        <v>0.05863442269018658</v>
+        <v>0.05863441512295105</v>
       </c>
       <c r="M106">
         <v>0.05539324905786337</v>
@@ -6015,16 +6651,22 @@
       <c r="P106">
         <v>0.03121954299366901</v>
       </c>
-    </row>
-    <row r="107" spans="1:16">
+      <c r="Q106">
+        <v>0.134100105318837</v>
+      </c>
+      <c r="R106">
+        <v>0.3282945133499804</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18">
       <c r="A107" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B107" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C107" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D107">
         <v>11.6776008605957</v>
@@ -6065,16 +6707,22 @@
       <c r="P107">
         <v>0.01009025481941429</v>
       </c>
-    </row>
-    <row r="108" spans="1:16">
+      <c r="Q107">
+        <v>0.1003687597176857</v>
+      </c>
+      <c r="R107">
+        <v>0.5354878651867594</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18">
       <c r="A108" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B108" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C108" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D108">
         <v>10.71059417724609</v>
@@ -6115,16 +6763,22 @@
       <c r="P108">
         <v>0.006312705272030632</v>
       </c>
-    </row>
-    <row r="109" spans="1:16">
+      <c r="Q108">
+        <v>0.08698654529963099</v>
+      </c>
+      <c r="R108">
+        <v>0.5979844656795172</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18">
       <c r="A109" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B109" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C109" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D109">
         <v>8.623311042785645</v>
@@ -6165,25 +6819,31 @@
       <c r="P109">
         <v>0.006624808328219321</v>
       </c>
-    </row>
-    <row r="110" spans="1:16">
+      <c r="Q109">
+        <v>0.08475595561973394</v>
+      </c>
+      <c r="R109">
+        <v>0.5719187304212743</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18">
       <c r="A110" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B110" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C110" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D110">
-        <v>11.49080181121826</v>
+        <v>11.49080276489258</v>
       </c>
       <c r="E110">
         <v>1000000000</v>
       </c>
       <c r="F110">
-        <v>11490801811.21826</v>
+        <v>11490802764.89258</v>
       </c>
       <c r="G110">
         <v>313784</v>
@@ -6195,13 +6855,13 @@
         <v>15483511</v>
       </c>
       <c r="J110">
-        <v>11490043775.21826</v>
+        <v>11490044728.89258</v>
       </c>
       <c r="K110">
         <v>0.02130892212305545</v>
       </c>
       <c r="L110">
-        <v>2.730920840151799E-05</v>
+        <v>2.730920613485226E-05</v>
       </c>
       <c r="M110">
         <v>0.01485141193105362</v>
@@ -6215,16 +6875,22 @@
       <c r="P110">
         <v>0.01325830258302583</v>
       </c>
-    </row>
-    <row r="111" spans="1:16">
+      <c r="Q110">
+        <v>0.08155615774907748</v>
+      </c>
+      <c r="R110">
+        <v>0.02071079335793358</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18">
       <c r="A111" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B111" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C111" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D111">
         <v>12.40600967407227</v>
@@ -6265,16 +6931,22 @@
       <c r="P111">
         <v>0.01104718469913997</v>
       </c>
-    </row>
-    <row r="112" spans="1:16">
+      <c r="Q111">
+        <v>0.08680885251100523</v>
+      </c>
+      <c r="R111">
+        <v>0.05327701473153273</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18">
       <c r="A112" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B112" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C112" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D112">
         <v>11.88656711578369</v>
@@ -6315,25 +6987,31 @@
       <c r="P112">
         <v>-0.05493720425768642</v>
       </c>
-    </row>
-    <row r="113" spans="1:16">
+      <c r="Q112">
+        <v>0.1066204523878677</v>
+      </c>
+      <c r="R112">
+        <v>0.02615658436468903</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18">
       <c r="A113" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B113" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C113" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D113">
-        <v>15.46859264373779</v>
+        <v>15.46859169006348</v>
       </c>
       <c r="E113">
         <v>13044201261</v>
       </c>
       <c r="F113">
-        <v>201775435669.3398</v>
+        <v>201775423229.4201</v>
       </c>
       <c r="G113">
         <v>60197000</v>
@@ -6345,13 +7023,13 @@
         <v>402084000</v>
       </c>
       <c r="J113">
-        <v>202318554669.3398</v>
+        <v>202318542229.4201</v>
       </c>
       <c r="K113">
         <v>0.06368684822202214</v>
       </c>
       <c r="L113">
-        <v>0.0002975357356540196</v>
+        <v>0.0002975357539485398</v>
       </c>
       <c r="M113">
         <v>0.09527113737428</v>
@@ -6365,25 +7043,31 @@
       <c r="P113">
         <v>0.03047622533010541</v>
       </c>
-    </row>
-    <row r="114" spans="1:16">
+      <c r="Q113">
+        <v>0.1106395098600021</v>
+      </c>
+      <c r="R113">
+        <v>0.4339101012214517</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18">
       <c r="A114" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B114" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C114" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D114">
-        <v>22.7707576751709</v>
+        <v>22.77076148986816</v>
       </c>
       <c r="E114">
         <v>13044201261</v>
       </c>
       <c r="F114">
-        <v>297026345980.3896</v>
+        <v>297026395740.0685</v>
       </c>
       <c r="G114">
         <v>41971000</v>
@@ -6395,13 +7079,13 @@
         <v>370683000</v>
       </c>
       <c r="J114">
-        <v>297560191980.3896</v>
+        <v>297560241740.0685</v>
       </c>
       <c r="K114">
         <v>0.04640094457999688</v>
       </c>
       <c r="L114">
-        <v>0.0001410504534247849</v>
+        <v>0.0001410504298375434</v>
       </c>
       <c r="M114">
         <v>0.07806130844953775</v>
@@ -6415,25 +7099,31 @@
       <c r="P114">
         <v>0.02313325445300758</v>
       </c>
-    </row>
-    <row r="115" spans="1:16">
+      <c r="Q114">
+        <v>0.0910108407150395</v>
+      </c>
+      <c r="R114">
+        <v>0.4283977167343545</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18">
       <c r="A115" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B115" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C115" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D115">
-        <v>26.97377777099609</v>
+        <v>26.97377967834473</v>
       </c>
       <c r="E115">
         <v>13015465561</v>
       </c>
       <c r="F115">
-        <v>351076275628.467</v>
+        <v>351076300453.4974</v>
       </c>
       <c r="G115">
         <v>47546000</v>
@@ -6445,13 +7135,13 @@
         <v>386007000</v>
       </c>
       <c r="J115">
-        <v>351638506628.467</v>
+        <v>351638531453.4974</v>
       </c>
       <c r="K115">
         <v>0.05014142019197712</v>
       </c>
       <c r="L115">
-        <v>0.0001352127230202237</v>
+        <v>0.0001352127134744553</v>
       </c>
       <c r="M115">
         <v>0.06932516767830635</v>
@@ -6465,16 +7155,22 @@
       <c r="P115">
         <v>0.02082765813376089</v>
       </c>
-    </row>
-    <row r="116" spans="1:16">
+      <c r="Q115">
+        <v>0.0971552656771713</v>
+      </c>
+      <c r="R115">
+        <v>0.4393382782157951</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18">
       <c r="A116" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B116" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C116" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D116">
         <v>12.16481018066406</v>
@@ -6515,16 +7211,22 @@
       <c r="P116">
         <v>-0.01368704722957133</v>
       </c>
-    </row>
-    <row r="117" spans="1:16">
+      <c r="Q116">
+        <v>0.1883409170125959</v>
+      </c>
+      <c r="R116">
+        <v>0.3810221469459141</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18">
       <c r="A117" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B117" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C117" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D117">
         <v>10.45218563079834</v>
@@ -6565,16 +7267,22 @@
       <c r="P117">
         <v>0.004946956309947563</v>
       </c>
-    </row>
-    <row r="118" spans="1:16">
+      <c r="Q117">
+        <v>0.1918921136123946</v>
+      </c>
+      <c r="R117">
+        <v>0.4003955532468432</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18">
       <c r="A118" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B118" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C118" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D118">
         <v>10.46080303192139</v>
@@ -6615,25 +7323,31 @@
       <c r="P118">
         <v>0.001526865853313587</v>
       </c>
-    </row>
-    <row r="119" spans="1:16">
+      <c r="Q118">
+        <v>0.1870875318893049</v>
+      </c>
+      <c r="R118">
+        <v>0.3938012448276944</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18">
       <c r="A119" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B119" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C119" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D119">
-        <v>12.25383472442627</v>
+        <v>12.25383377075195</v>
       </c>
       <c r="E119">
         <v>1095147387</v>
       </c>
       <c r="F119">
-        <v>13419755079.1853</v>
+        <v>13419754034.77136</v>
       </c>
       <c r="G119">
         <v>677839</v>
@@ -6645,13 +7359,13 @@
         <v>11891864</v>
       </c>
       <c r="J119">
-        <v>13419638126.1853</v>
+        <v>13419637081.77136</v>
       </c>
       <c r="K119">
         <v>0.05756637990724516</v>
       </c>
       <c r="L119">
-        <v>5.051097456028678E-05</v>
+        <v>5.051097849141885E-05</v>
       </c>
       <c r="M119">
         <v>0.02302624718883432</v>
@@ -6665,25 +7379,31 @@
       <c r="P119">
         <v>0.02230763741162485</v>
       </c>
-    </row>
-    <row r="120" spans="1:16">
+      <c r="Q119">
+        <v>2.48895253615821</v>
+      </c>
+      <c r="R119">
+        <v>0.0005954405983440739</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18">
       <c r="A120" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C120" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D120">
-        <v>16.58129692077637</v>
+        <v>16.58129501342773</v>
       </c>
       <c r="E120">
         <v>1095183775</v>
       </c>
       <c r="F120">
-        <v>18159567356.09174</v>
+        <v>18159565267.19446</v>
       </c>
       <c r="G120">
         <v>514602</v>
@@ -6695,13 +7415,13 @@
         <v>12096581</v>
       </c>
       <c r="J120">
-        <v>18159543312.09174</v>
+        <v>18159541223.19446</v>
       </c>
       <c r="K120">
         <v>0.04262583746895951</v>
       </c>
       <c r="L120">
-        <v>2.833782717747899E-05</v>
+        <v>2.833783043718744E-05</v>
       </c>
       <c r="M120">
         <v>0.01973210446819643</v>
@@ -6715,16 +7435,22 @@
       <c r="P120">
         <v>0.01912907265458869</v>
       </c>
-    </row>
-    <row r="121" spans="1:16">
+      <c r="Q120">
+        <v>2.371592760907709</v>
+      </c>
+      <c r="R120">
+        <v>0.0005999398297055646</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18">
       <c r="A121" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C121" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D121">
         <v>16.68288421630859</v>
@@ -6765,25 +7491,31 @@
       <c r="P121">
         <v>0.06798743483167247</v>
       </c>
-    </row>
-    <row r="122" spans="1:16">
+      <c r="Q121">
+        <v>2.477968732323605</v>
+      </c>
+      <c r="R121">
+        <v>0.000594251082295994</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18">
       <c r="A122" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B122" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C122" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D122">
-        <v>61.1424560546875</v>
+        <v>61.14244079589844</v>
       </c>
       <c r="E122">
         <v>4439999</v>
       </c>
       <c r="F122">
-        <v>271472443.7403564</v>
+        <v>271472375.9913483</v>
       </c>
       <c r="G122">
         <v>14671000</v>
@@ -6795,13 +7527,13 @@
         <v>189678000</v>
       </c>
       <c r="J122">
-        <v>282533443.7403564</v>
+        <v>282533375.9913483</v>
       </c>
       <c r="K122">
         <v>0.07308495110566457</v>
       </c>
       <c r="L122">
-        <v>0.05192659603683027</v>
+        <v>0.05192660848836937</v>
       </c>
       <c r="M122">
         <v>0.05131855038538997</v>
@@ -6815,25 +7547,31 @@
       <c r="P122">
         <v>0.02274538210793191</v>
       </c>
-    </row>
-    <row r="123" spans="1:16">
+      <c r="Q122">
+        <v>0.1024430138682805</v>
+      </c>
+      <c r="R122">
+        <v>0.0424881120678576</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18">
       <c r="A123" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C123" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D123">
-        <v>48.90481948852539</v>
+        <v>48.90482330322266</v>
       </c>
       <c r="E123">
         <v>4343393</v>
       </c>
       <c r="F123">
-        <v>212412850.6327248</v>
+        <v>212412867.2014542</v>
       </c>
       <c r="G123">
         <v>14208000</v>
@@ -6845,13 +7583,13 @@
         <v>186988000</v>
       </c>
       <c r="J123">
-        <v>224870850.6327248</v>
+        <v>224870867.2014542</v>
       </c>
       <c r="K123">
         <v>0.07123732739688939</v>
       </c>
       <c r="L123">
-        <v>0.06318293349281418</v>
+        <v>0.06318292883742711</v>
       </c>
       <c r="M123">
         <v>0.02541339551201147</v>
@@ -6865,25 +7603,31 @@
       <c r="P123">
         <v>0.01150243264831893</v>
       </c>
-    </row>
-    <row r="124" spans="1:16">
+      <c r="Q123">
+        <v>0.1156004163338416</v>
+      </c>
+      <c r="R123">
+        <v>0.04214411928448673</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18">
       <c r="A124" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B124" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C124" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D124">
-        <v>53.01611328125</v>
+        <v>53.01611709594727</v>
       </c>
       <c r="E124">
         <v>4302854</v>
       </c>
       <c r="F124">
-        <v>228120595.0966797</v>
+        <v>228120611.5107651</v>
       </c>
       <c r="G124">
         <v>16499000</v>
@@ -6895,13 +7639,13 @@
         <v>190172000</v>
       </c>
       <c r="J124">
-        <v>244373595.0966797</v>
+        <v>244373611.5107651</v>
       </c>
       <c r="K124">
         <v>0.0799273343829478</v>
       </c>
       <c r="L124">
-        <v>0.06751547765818408</v>
+        <v>0.06751547312330484</v>
       </c>
       <c r="M124">
         <v>0.07343878173442989</v>
@@ -6915,25 +7659,31 @@
       <c r="P124">
         <v>0.03357558593796955</v>
       </c>
-    </row>
-    <row r="125" spans="1:16">
+      <c r="Q124">
+        <v>0.1249215664119128</v>
+      </c>
+      <c r="R124">
+        <v>0.04455027803354673</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18">
       <c r="A125" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B125" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C125" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D125">
-        <v>18.18595123291016</v>
+        <v>18.18594932556152</v>
       </c>
       <c r="E125">
         <v>1749090403</v>
       </c>
       <c r="F125">
-        <v>31808872770.90917</v>
+        <v>31808869434.78398</v>
       </c>
       <c r="G125">
         <v>4292437</v>
@@ -6945,13 +7695,13 @@
         <v>48618148</v>
       </c>
       <c r="J125">
-        <v>31810328084.90917</v>
+        <v>31810324748.78398</v>
       </c>
       <c r="K125">
         <v>0.08572279264413553</v>
       </c>
       <c r="L125">
-        <v>0.0001349384699378921</v>
+        <v>0.0001349384840896378</v>
       </c>
       <c r="M125">
         <v>0.06613577711763105</v>
@@ -6965,16 +7715,22 @@
       <c r="P125">
         <v>0.05849683641427562</v>
       </c>
-    </row>
-    <row r="126" spans="1:16">
+      <c r="Q125">
+        <v>0.3433384228058922</v>
+      </c>
+      <c r="R125">
+        <v>0.02692454451537137</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18">
       <c r="A126" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B126" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C126" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D126">
         <v>18.41227912902832</v>
@@ -7015,16 +7771,22 @@
       <c r="P126">
         <v>0.03969973486116229</v>
       </c>
-    </row>
-    <row r="127" spans="1:16">
+      <c r="Q126">
+        <v>0.3384153463331601</v>
+      </c>
+      <c r="R126">
+        <v>0.0170328506545615</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18">
       <c r="A127" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B127" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C127" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D127">
         <v>18.02587699890137</v>
@@ -7065,25 +7827,31 @@
       <c r="P127">
         <v>0.02883086576007799</v>
       </c>
-    </row>
-    <row r="128" spans="1:16">
+      <c r="Q127">
+        <v>0.3090002611875626</v>
+      </c>
+      <c r="R127">
+        <v>0.01801602014369463</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18">
       <c r="A128" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B128" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C128" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D128">
-        <v>20.22709465026855</v>
+        <v>20.22709274291992</v>
       </c>
       <c r="E128">
         <v>235323269</v>
       </c>
       <c r="F128">
-        <v>4759906035.473608</v>
+        <v>4759905586.630093</v>
       </c>
       <c r="G128">
         <v>48234037</v>
@@ -7095,13 +7863,13 @@
         <v>1692088553</v>
       </c>
       <c r="J128">
-        <v>4759591574.473608</v>
+        <v>4759591125.630093</v>
       </c>
       <c r="K128">
         <v>0.02851092071222001</v>
       </c>
       <c r="L128">
-        <v>0.01013407059099068</v>
+        <v>0.0101340715466635</v>
       </c>
       <c r="M128">
         <v>0.02279500616655965</v>
@@ -7115,16 +7883,22 @@
       <c r="P128">
         <v>0.02165974118882981</v>
       </c>
-    </row>
-    <row r="129" spans="1:16">
+      <c r="Q128">
+        <v>0.2199195044299435</v>
+      </c>
+      <c r="R128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18">
       <c r="A129" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B129" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C129" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D129">
         <v>26.53553581237793</v>
@@ -7165,25 +7939,31 @@
       <c r="P129">
         <v>0.06085724268200526</v>
       </c>
-    </row>
-    <row r="130" spans="1:16">
+      <c r="Q129">
+        <v>0.3098126829529463</v>
+      </c>
+      <c r="R129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18">
       <c r="A130" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B130" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C130" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D130">
-        <v>25.02614212036133</v>
+        <v>25.0261402130127</v>
       </c>
       <c r="E130">
         <v>235200814</v>
       </c>
       <c r="F130">
-        <v>5886168997.98867</v>
+        <v>5886168549.378719</v>
       </c>
       <c r="G130">
         <v>87218592</v>
@@ -7195,13 +7975,13 @@
         <v>1876600039</v>
       </c>
       <c r="J130">
-        <v>5885973272.98867</v>
+        <v>5885972824.378719</v>
       </c>
       <c r="K130">
         <v>0.04648176906717557</v>
       </c>
       <c r="L130">
-        <v>0.01481804078184571</v>
+        <v>0.01481804191122921</v>
       </c>
       <c r="M130">
         <v>0.04078591517070729</v>
@@ -7215,16 +7995,22 @@
       <c r="P130">
         <v>0.0407041540270543</v>
       </c>
-    </row>
-    <row r="131" spans="1:16">
+      <c r="Q130">
+        <v>0.2432025400011991</v>
+      </c>
+      <c r="R130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18">
       <c r="A131" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B131" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C131" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D131">
         <v>11.01731967926025</v>
@@ -7265,25 +8051,31 @@
       <c r="P131">
         <v>0.00202961737953845</v>
       </c>
-    </row>
-    <row r="132" spans="1:16">
+      <c r="Q131">
+        <v>0.9781502919141046</v>
+      </c>
+      <c r="R131">
+        <v>0.4253927685484477</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18">
       <c r="A132" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B132" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C132" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D132">
-        <v>13.80032253265381</v>
+        <v>13.80032062530518</v>
       </c>
       <c r="E132">
         <v>1114904</v>
       </c>
       <c r="F132">
-        <v>15386034.79294586</v>
+        <v>15386032.66643524</v>
       </c>
       <c r="G132">
         <v>524000</v>
@@ -7295,13 +8087,13 @@
         <v>12818000</v>
       </c>
       <c r="J132">
-        <v>26742034.79294586</v>
+        <v>26742032.66643524</v>
       </c>
       <c r="K132">
         <v>0.02167618102093158</v>
       </c>
       <c r="L132">
-        <v>0.01959461963373943</v>
+        <v>0.01959462119189199</v>
       </c>
       <c r="M132">
         <v>0.01037603370260571</v>
@@ -7315,25 +8107,31 @@
       <c r="P132">
         <v>0.003400403957763404</v>
       </c>
-    </row>
-    <row r="133" spans="1:16">
+      <c r="Q132">
+        <v>0.9506813591389052</v>
+      </c>
+      <c r="R132">
+        <v>0.4249993608263237</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18">
       <c r="A133" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B133" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C133" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D133">
-        <v>14.79028129577637</v>
+        <v>14.79027938842773</v>
       </c>
       <c r="E133">
         <v>1114904</v>
       </c>
       <c r="F133">
-        <v>16489743.77778625</v>
+        <v>16489741.65127563</v>
       </c>
       <c r="G133">
         <v>2083000</v>
@@ -7345,13 +8143,13 @@
         <v>13555000</v>
       </c>
       <c r="J133">
-        <v>26333743.77778625</v>
+        <v>26333741.65127563</v>
       </c>
       <c r="K133">
         <v>0.08902089832898842</v>
       </c>
       <c r="L133">
-        <v>0.07910003293026295</v>
+        <v>0.07910003931777379</v>
       </c>
       <c r="M133">
         <v>0.09258576171154556</v>
@@ -7365,16 +8163,22 @@
       <c r="P133">
         <v>0.03117702588562627</v>
       </c>
-    </row>
-    <row r="134" spans="1:16">
+      <c r="Q133">
+        <v>1.069781885030059</v>
+      </c>
+      <c r="R133">
+        <v>0.390644408009142</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18">
       <c r="A134" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B134" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C134" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D134">
         <v>19.36000061035156</v>
@@ -7415,16 +8219,22 @@
       <c r="P134">
         <v>0.003203188941271857</v>
       </c>
-    </row>
-    <row r="135" spans="1:16">
+      <c r="Q134">
+        <v>0.2569184563495748</v>
+      </c>
+      <c r="R134">
+        <v>0.1162393810338893</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18">
       <c r="A135" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B135" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C135" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D135">
         <v>27.86000061035156</v>
@@ -7465,16 +8275,22 @@
       <c r="P135">
         <v>-0.01106128308293587</v>
       </c>
-    </row>
-    <row r="136" spans="1:16">
+      <c r="Q135">
+        <v>0.2385456699569502</v>
+      </c>
+      <c r="R135">
+        <v>0.1206134587587049</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18">
       <c r="A136" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B136" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C136" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D136">
         <v>20.52000045776367</v>
@@ -7515,16 +8331,22 @@
       <c r="P136">
         <v>-0.03341999181775289</v>
       </c>
-    </row>
-    <row r="137" spans="1:16">
+      <c r="Q136">
+        <v>0.2178557717927776</v>
+      </c>
+      <c r="R136">
+        <v>0.120339442409189</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18">
       <c r="A137" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B137" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C137" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D137">
         <v>2.557408809661865</v>
@@ -7565,25 +8387,31 @@
       <c r="P137">
         <v>-0.01436363003867302</v>
       </c>
-    </row>
-    <row r="138" spans="1:16">
+      <c r="Q137">
+        <v>0.1410337329931605</v>
+      </c>
+      <c r="R137">
+        <v>0.2290338885128475</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18">
       <c r="A138" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B138" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C138" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D138">
-        <v>4.977323055267334</v>
+        <v>4.977322578430176</v>
       </c>
       <c r="E138">
         <v>305594568</v>
       </c>
       <c r="F138">
-        <v>1521042888.870861</v>
+        <v>1521042743.152016</v>
       </c>
       <c r="G138">
         <v>101931</v>
@@ -7595,13 +8423,13 @@
         <v>2878202</v>
       </c>
       <c r="J138">
-        <v>1522036544.870861</v>
+        <v>1522036399.152016</v>
       </c>
       <c r="K138">
         <v>0.02632612043106953</v>
       </c>
       <c r="L138">
-        <v>6.697013967470043E-05</v>
+        <v>6.697014608638114E-05</v>
       </c>
       <c r="M138">
         <v>0.001467582886816144</v>
@@ -7615,16 +8443,22 @@
       <c r="P138">
         <v>0.0004853034847179955</v>
       </c>
-    </row>
-    <row r="139" spans="1:16">
+      <c r="Q138">
+        <v>0.1887629494686938</v>
+      </c>
+      <c r="R138">
+        <v>0.1965525069877268</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18">
       <c r="A139" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B139" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C139" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D139">
         <v>5.041487216949463</v>
@@ -7665,16 +8499,22 @@
       <c r="P139">
         <v>-0.005076694571534647</v>
       </c>
-    </row>
-    <row r="140" spans="1:16">
+      <c r="Q139">
+        <v>0.1770995177702678</v>
+      </c>
+      <c r="R139">
+        <v>0.197816017980467</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18">
       <c r="A140" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B140" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C140" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D140">
         <v>14.72999954223633</v>
@@ -7715,16 +8555,22 @@
       <c r="P140">
         <v>-0.00644287319103945</v>
       </c>
-    </row>
-    <row r="141" spans="1:16">
+      <c r="Q140">
+        <v>0.1485495275226326</v>
+      </c>
+      <c r="R140">
+        <v>0.2167448622216348</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18">
       <c r="A141" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B141" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C141" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D141">
         <v>18.70999908447266</v>
@@ -7765,16 +8611,22 @@
       <c r="P141">
         <v>-0.01170329487648369</v>
       </c>
-    </row>
-    <row r="142" spans="1:16">
+      <c r="Q141">
+        <v>0.1580942248229544</v>
+      </c>
+      <c r="R141">
+        <v>0.2047744123416564</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18">
       <c r="A142" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B142" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C142" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D142">
         <v>3.5</v>
@@ -7815,16 +8667,22 @@
       <c r="P142">
         <v>-0.0568598841579343</v>
       </c>
-    </row>
-    <row r="143" spans="1:16">
+      <c r="Q142">
+        <v>0.209665296016271</v>
+      </c>
+      <c r="R142">
+        <v>0.2675421143387717</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18">
       <c r="A143" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B143" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C143" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D143">
         <v>28.35722351074219</v>
@@ -7865,16 +8723,22 @@
       <c r="P143">
         <v>-0.01300718914503268</v>
       </c>
-    </row>
-    <row r="144" spans="1:16">
+      <c r="Q143">
+        <v>0.3014677851628255</v>
+      </c>
+      <c r="R143">
+        <v>0.2280339086400404</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18">
       <c r="A144" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B144" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C144" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D144">
         <v>28.87125205993652</v>
@@ -7915,16 +8779,22 @@
       <c r="P144">
         <v>-0.009614434862559074</v>
       </c>
-    </row>
-    <row r="145" spans="1:16">
+      <c r="Q144">
+        <v>0.2731350106950257</v>
+      </c>
+      <c r="R144">
+        <v>0.2168259524295354</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18">
       <c r="A145" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B145" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C145" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D145">
         <v>18.16232872009277</v>
@@ -7965,16 +8835,22 @@
       <c r="P145">
         <v>-0.01535330769919717</v>
       </c>
-    </row>
-    <row r="146" spans="1:16">
+      <c r="Q145">
+        <v>0.2643092578199412</v>
+      </c>
+      <c r="R145">
+        <v>0.2153721261535199</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18">
       <c r="A146" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B146" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C146" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D146">
         <v>14.19134616851807</v>
@@ -8015,16 +8891,22 @@
       <c r="P146">
         <v>-0.01088625234837931</v>
       </c>
-    </row>
-    <row r="147" spans="1:16">
+      <c r="Q146">
+        <v>0.2503965690985143</v>
+      </c>
+      <c r="R146">
+        <v>0.1413124634839902</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18">
       <c r="A147" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B147" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C147" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D147">
         <v>17.2528190612793</v>
@@ -8065,16 +8947,22 @@
       <c r="P147">
         <v>-0.01170546553148482</v>
       </c>
-    </row>
-    <row r="148" spans="1:16">
+      <c r="Q147">
+        <v>0.2622930236142316</v>
+      </c>
+      <c r="R147">
+        <v>0.1972693788835646</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18">
       <c r="A148" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B148" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C148" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D148">
         <v>16.55729484558105</v>
@@ -8115,16 +9003,22 @@
       <c r="P148">
         <v>0.04317364233569708</v>
       </c>
-    </row>
-    <row r="149" spans="1:16">
+      <c r="Q148">
+        <v>0.256330150279665</v>
+      </c>
+      <c r="R148">
+        <v>0.2112754247224224</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18">
       <c r="A149" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B149" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C149" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D149">
         <v>26.77040100097656</v>
@@ -8165,16 +9059,22 @@
       <c r="P149">
         <v>0.01441605123261315</v>
       </c>
-    </row>
-    <row r="150" spans="1:16">
+      <c r="Q149">
+        <v>0.1541053531575579</v>
+      </c>
+      <c r="R149">
+        <v>0.2420207177425883</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18">
       <c r="A150" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B150" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C150" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D150">
         <v>28.50059127807617</v>
@@ -8215,25 +9115,31 @@
       <c r="P150">
         <v>0.01446363022821734</v>
       </c>
-    </row>
-    <row r="151" spans="1:16">
+      <c r="Q150">
+        <v>0.1514499964361923</v>
+      </c>
+      <c r="R150">
+        <v>0.2399131711652315</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18">
       <c r="A151" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B151" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C151" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D151">
-        <v>25.87128639221191</v>
+        <v>25.87128448486328</v>
       </c>
       <c r="E151">
         <v>603799719</v>
       </c>
       <c r="F151">
-        <v>15621075453.78608</v>
+        <v>15621074302.12951</v>
       </c>
       <c r="G151">
         <v>206470</v>
@@ -8245,13 +9151,13 @@
         <v>4712485</v>
       </c>
       <c r="J151">
-        <v>15620843603.78608</v>
+        <v>15620842452.12951</v>
       </c>
       <c r="K151">
         <v>0.04608052206885854</v>
       </c>
       <c r="L151">
-        <v>1.32175960042233E-05</v>
+        <v>1.3217596978699E-05</v>
       </c>
       <c r="M151">
         <v>0.09226066502068442</v>
@@ -8265,16 +9171,22 @@
       <c r="P151">
         <v>0.05865771949711431</v>
       </c>
-    </row>
-    <row r="152" spans="1:16">
+      <c r="Q151">
+        <v>0.1556099740667357</v>
+      </c>
+      <c r="R151">
+        <v>0.2277262239510466</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18">
       <c r="A152" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B152" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C152" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D152">
         <v>17.59828567504883</v>
@@ -8315,16 +9227,22 @@
       <c r="P152">
         <v>0.01009267368172903</v>
       </c>
-    </row>
-    <row r="153" spans="1:16">
+      <c r="Q152">
+        <v>0.05524087609354014</v>
+      </c>
+      <c r="R152">
+        <v>0.1440372142268525</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18">
       <c r="A153" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B153" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C153" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D153">
         <v>20.74707412719727</v>
@@ -8365,16 +9283,22 @@
       <c r="P153">
         <v>0.01616768607465542</v>
       </c>
-    </row>
-    <row r="154" spans="1:16">
+      <c r="Q153">
+        <v>0.06147940223400107</v>
+      </c>
+      <c r="R153">
+        <v>0.1407343846102331</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18">
       <c r="A154" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B154" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C154" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D154">
         <v>18.73899269104004</v>
@@ -8415,25 +9339,31 @@
       <c r="P154">
         <v>0.0124753246869705</v>
       </c>
-    </row>
-    <row r="155" spans="1:16">
+      <c r="Q154">
+        <v>0.05697220509154169</v>
+      </c>
+      <c r="R154">
+        <v>0.1405855961796114</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18">
       <c r="A155" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B155" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C155" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D155">
-        <v>11.39059257507324</v>
+        <v>11.39059162139893</v>
       </c>
       <c r="E155">
         <v>366830452</v>
       </c>
       <c r="F155">
-        <v>4178416222.861961</v>
+        <v>4178415873.025181</v>
       </c>
       <c r="G155">
         <v>214518</v>
@@ -8445,13 +9375,13 @@
         <v>2785864</v>
       </c>
       <c r="J155">
-        <v>4181995555.861961</v>
+        <v>4181995206.025181</v>
       </c>
       <c r="K155">
         <v>0.03370170632582149</v>
       </c>
       <c r="L155">
-        <v>5.129560687822997E-05</v>
+        <v>5.129561116926549E-05</v>
       </c>
       <c r="M155">
         <v>0.03367860024753541</v>
@@ -8465,25 +9395,31 @@
       <c r="P155">
         <v>0.01281895036099751</v>
       </c>
-    </row>
-    <row r="156" spans="1:16">
+      <c r="Q155">
+        <v>0.1689841899976555</v>
+      </c>
+      <c r="R155">
+        <v>0.4895176552950583</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18">
       <c r="A156" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B156" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C156" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D156">
-        <v>13.22038173675537</v>
+        <v>13.22038078308105</v>
       </c>
       <c r="E156">
         <v>546800709</v>
       </c>
       <c r="F156">
-        <v>7228914106.908488</v>
+        <v>7228913585.438696</v>
       </c>
       <c r="G156">
         <v>197757</v>
@@ -8495,13 +9431,13 @@
         <v>5095380</v>
       </c>
       <c r="J156">
-        <v>7232219894.908488</v>
+        <v>7232219373.438696</v>
       </c>
       <c r="K156">
         <v>0.02353922692654164</v>
       </c>
       <c r="L156">
-        <v>2.734388650699376E-05</v>
+        <v>2.734388847858921E-05</v>
       </c>
       <c r="M156">
         <v>0.01453120277584793</v>
@@ -8515,16 +9451,22 @@
       <c r="P156">
         <v>0.007773676631346598</v>
       </c>
-    </row>
-    <row r="157" spans="1:16">
+      <c r="Q156">
+        <v>0.1742353676354173</v>
+      </c>
+      <c r="R156">
+        <v>0.3477079822289565</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18">
       <c r="A157" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B157" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C157" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D157">
         <v>12.62378215789795</v>
@@ -8565,16 +9507,22 @@
       <c r="P157">
         <v>0.01780797596582431</v>
       </c>
-    </row>
-    <row r="158" spans="1:16">
+      <c r="Q157">
+        <v>0.1938219747579382</v>
+      </c>
+      <c r="R157">
+        <v>0.3414116803017663</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18">
       <c r="A158" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B158" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C158" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D158">
         <v>6.721556663513184</v>
@@ -8615,16 +9563,22 @@
       <c r="P158">
         <v>0.0149381750274533</v>
       </c>
-    </row>
-    <row r="159" spans="1:16">
+      <c r="Q158">
+        <v>0.19920044153713</v>
+      </c>
+      <c r="R158">
+        <v>0.1679240528460771</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18">
       <c r="A159" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B159" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C159" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D159">
         <v>6.834285259246826</v>
@@ -8665,16 +9619,22 @@
       <c r="P159">
         <v>0.007932818791612811</v>
       </c>
-    </row>
-    <row r="160" spans="1:16">
+      <c r="Q159">
+        <v>0.1901344474436986</v>
+      </c>
+      <c r="R159">
+        <v>0.1628931460017193</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18">
       <c r="A160" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B160" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C160" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D160">
         <v>6.418621063232422</v>
@@ -8715,25 +9675,31 @@
       <c r="P160">
         <v>-0.004538669761847978</v>
       </c>
-    </row>
-    <row r="161" spans="1:16">
+      <c r="Q160">
+        <v>0.1840347728775217</v>
+      </c>
+      <c r="R160">
+        <v>0.166402550948066</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18">
       <c r="A161" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C161" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D161">
-        <v>5.427212715148926</v>
+        <v>5.417028427124023</v>
       </c>
       <c r="E161">
         <v>9701410</v>
       </c>
       <c r="F161">
-        <v>52651615.70687294</v>
+        <v>52552813.75318527</v>
       </c>
       <c r="G161">
         <v>3323000</v>
@@ -8745,13 +9711,13 @@
         <v>73632000</v>
       </c>
       <c r="J161">
-        <v>56595615.70687294</v>
+        <v>56496813.75318527</v>
       </c>
       <c r="K161">
         <v>0.04283541301433433</v>
       </c>
       <c r="L161">
-        <v>0.05871479545714098</v>
+        <v>0.0588174762300228</v>
       </c>
       <c r="M161">
         <v>0.03933072577140374</v>
@@ -8765,25 +9731,31 @@
       <c r="P161">
         <v>0.03426529573931872</v>
       </c>
-    </row>
-    <row r="162" spans="1:16">
+      <c r="Q161">
+        <v>0.0202562798016967</v>
+      </c>
+      <c r="R161">
+        <v>0.07909651312753647</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18">
       <c r="A162" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C162" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D162">
-        <v>6.457475662231445</v>
+        <v>6.445357799530029</v>
       </c>
       <c r="E162">
         <v>9701410</v>
       </c>
       <c r="F162">
-        <v>62646618.96432877</v>
+        <v>62529058.60993862</v>
       </c>
       <c r="G162">
         <v>4141000</v>
@@ -8795,13 +9767,13 @@
         <v>76867000</v>
       </c>
       <c r="J162">
-        <v>65432618.96432877</v>
+        <v>65315058.60993862</v>
       </c>
       <c r="K162">
         <v>0.05198799794106939</v>
       </c>
       <c r="L162">
-        <v>0.06328647799131358</v>
+        <v>0.06340038711026874</v>
       </c>
       <c r="M162">
         <v>0.04801800512573666</v>
@@ -8815,25 +9787,31 @@
       <c r="P162">
         <v>0.04174253305135542</v>
       </c>
-    </row>
-    <row r="163" spans="1:16">
+      <c r="Q162">
+        <v>0.02209832283455662</v>
+      </c>
+      <c r="R162">
+        <v>0.0750370378747611</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18">
       <c r="A163" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C163" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D163">
-        <v>6.213871479034424</v>
+        <v>6.202213287353516</v>
       </c>
       <c r="E163">
         <v>9701410</v>
       </c>
       <c r="F163">
-        <v>60283314.90541935</v>
+        <v>60170214.00806427</v>
       </c>
       <c r="G163">
         <v>3622000</v>
@@ -8845,13 +9823,13 @@
         <v>79738000</v>
       </c>
       <c r="J163">
-        <v>62009314.90541935</v>
+        <v>61896214.00806427</v>
       </c>
       <c r="K163">
         <v>0.04446135716390062</v>
       </c>
       <c r="L163">
-        <v>0.05841057920934154</v>
+        <v>0.05851731092192651</v>
       </c>
       <c r="M163">
         <v>0.05371341142240839</v>
@@ -8865,25 +9843,31 @@
       <c r="P163">
         <v>0.04829452556802165</v>
       </c>
-    </row>
-    <row r="164" spans="1:16">
+      <c r="Q163">
+        <v>0.01994700343913853</v>
+      </c>
+      <c r="R163">
+        <v>0.05586063032079833</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18">
       <c r="A164" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B164" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C164" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D164">
-        <v>21.89017105102539</v>
+        <v>21.89017677307129</v>
       </c>
       <c r="E164">
         <v>1648444575</v>
       </c>
       <c r="F164">
-        <v>36084733714.88486</v>
+        <v>36084743147.36037</v>
       </c>
       <c r="G164">
         <v>432683</v>
@@ -8895,13 +9879,13 @@
         <v>5458659</v>
       </c>
       <c r="J164">
-        <v>36086610110.88486</v>
+        <v>36086619543.36037</v>
       </c>
       <c r="K164">
         <v>0.0589883784102505</v>
       </c>
       <c r="L164">
-        <v>1.199012594063218E-05</v>
+        <v>1.199012280660159E-05</v>
       </c>
       <c r="M164">
         <v>0.03627594249796516</v>
@@ -8915,25 +9899,31 @@
       <c r="P164">
         <v>0.01128336045367294</v>
       </c>
-    </row>
-    <row r="165" spans="1:16">
+      <c r="Q164">
+        <v>0.4519399034471465</v>
+      </c>
+      <c r="R164">
+        <v>0.1240757103924948</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18">
       <c r="A165" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C165" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D165">
-        <v>27.6666259765625</v>
+        <v>27.6666316986084</v>
       </c>
       <c r="E165">
         <v>1714382358</v>
       </c>
       <c r="F165">
-        <v>47431175479.60327</v>
+        <v>47431185289.37781</v>
       </c>
       <c r="G165">
         <v>642979</v>
@@ -8945,13 +9935,13 @@
         <v>5531976</v>
       </c>
       <c r="J165">
-        <v>47433106094.60327</v>
+        <v>47433115904.37781</v>
       </c>
       <c r="K165">
         <v>0.08616028936866565</v>
       </c>
       <c r="L165">
-        <v>1.355549009836308E-05</v>
+        <v>1.355548729491449E-05</v>
       </c>
       <c r="M165">
         <v>0.06201780340334087</v>
@@ -8965,25 +9955,31 @@
       <c r="P165">
         <v>0.02020551519202015</v>
       </c>
-    </row>
-    <row r="166" spans="1:16">
+      <c r="Q165">
+        <v>0.4972042287049402</v>
+      </c>
+      <c r="R165">
+        <v>0.1292615031756984</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18">
       <c r="A166" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C166" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D166">
-        <v>25.86973190307617</v>
+        <v>25.8697338104248</v>
       </c>
       <c r="E166">
         <v>1714382358</v>
       </c>
       <c r="F166">
-        <v>44350611980.82355</v>
+        <v>44350615250.7484</v>
       </c>
       <c r="G166">
         <v>530139</v>
@@ -8995,13 +9991,13 @@
         <v>5721825</v>
       </c>
       <c r="J166">
-        <v>44352949912.82355</v>
+        <v>44352953182.7484</v>
       </c>
       <c r="K166">
         <v>0.06577605255344547</v>
       </c>
       <c r="L166">
-        <v>1.195273371989906E-05</v>
+        <v>1.195273283868285E-05</v>
       </c>
       <c r="M166">
         <v>0.04686354441109261</v>
@@ -9015,25 +10011,31 @@
       <c r="P166">
         <v>0.01442954192090139</v>
       </c>
-    </row>
-    <row r="167" spans="1:16">
+      <c r="Q166">
+        <v>0.4668666194157398</v>
+      </c>
+      <c r="R166">
+        <v>0.1543927890873929</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18">
       <c r="A167" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B167" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C167" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D167">
-        <v>9.65755558013916</v>
+        <v>9.657556533813477</v>
       </c>
       <c r="E167">
         <v>584930207</v>
       </c>
       <c r="F167">
-        <v>5648995984.604804</v>
+        <v>5648996542.437719</v>
       </c>
       <c r="G167">
         <v>400861</v>
@@ -9045,13 +10047,13 @@
         <v>533467</v>
       </c>
       <c r="J167">
-        <v>5658537759.604804</v>
+        <v>5658538317.437719</v>
       </c>
       <c r="K167">
         <v>0.03978673663620189</v>
       </c>
       <c r="L167">
-        <v>7.084179995433951E-05</v>
+        <v>7.0841792970577E-05</v>
       </c>
       <c r="M167">
         <v>0.2136289592420899</v>
@@ -9065,16 +10067,22 @@
       <c r="P167">
         <v>0.005674965556020541</v>
       </c>
-    </row>
-    <row r="168" spans="1:16">
+      <c r="Q167">
+        <v>0.3177726253174254</v>
+      </c>
+      <c r="R167">
+        <v>0.6503814582336996</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18">
       <c r="A168" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B168" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C168" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D168">
         <v>10.08974361419678</v>
@@ -9115,16 +10123,22 @@
       <c r="P168">
         <v>0.006174041258563061</v>
       </c>
-    </row>
-    <row r="169" spans="1:16">
+      <c r="Q168">
+        <v>0.3721076952194341</v>
+      </c>
+      <c r="R168">
+        <v>0.6568880841750331</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18">
       <c r="A169" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B169" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C169" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D169">
         <v>7.806974411010742</v>
@@ -9165,16 +10179,22 @@
       <c r="P169">
         <v>0.005365518964733755</v>
       </c>
-    </row>
-    <row r="170" spans="1:16">
+      <c r="Q169">
+        <v>0.2688955660535572</v>
+      </c>
+      <c r="R169">
+        <v>0.714788237259979</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18">
       <c r="A170" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B170" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C170" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E170">
         <v>920205</v>
@@ -9203,16 +10223,22 @@
       <c r="P170">
         <v>-0.0006660555177733948</v>
       </c>
-    </row>
-    <row r="171" spans="1:16">
+      <c r="Q170">
+        <v>0.2140875206481867</v>
+      </c>
+      <c r="R170">
+        <v>0.4107132556770702</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18">
       <c r="A171" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B171" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C171" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E171">
         <v>920205</v>
@@ -9241,16 +10267,22 @@
       <c r="P171">
         <v>0.001624908531107995</v>
       </c>
-    </row>
-    <row r="172" spans="1:16">
+      <c r="Q171">
+        <v>0.2661357131582196</v>
+      </c>
+      <c r="R171">
+        <v>0.4261708353467812</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18">
       <c r="A172" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B172" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C172" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E172">
         <v>920205</v>
@@ -9279,16 +10311,22 @@
       <c r="P172">
         <v>0.3490515776413855</v>
       </c>
-    </row>
-    <row r="173" spans="1:16">
+      <c r="Q172">
+        <v>0.2175102615268027</v>
+      </c>
+      <c r="R172">
+        <v>0.1141127036504554</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18">
       <c r="A173" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B173" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C173" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E173">
         <v>374921</v>
@@ -9317,16 +10355,22 @@
       <c r="P173">
         <v>0.018209221341825</v>
       </c>
-    </row>
-    <row r="174" spans="1:16">
+      <c r="Q173">
+        <v>0.1223185811255788</v>
+      </c>
+      <c r="R173">
+        <v>0.2223187145543964</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18">
       <c r="A174" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C174" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E174">
         <v>374921</v>
@@ -9355,16 +10399,22 @@
       <c r="P174">
         <v>0.02942755628757561</v>
       </c>
-    </row>
-    <row r="175" spans="1:16">
+      <c r="Q174">
+        <v>0.1560159660196633</v>
+      </c>
+      <c r="R174">
+        <v>0.2088788533356007</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18">
       <c r="A175" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B175" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C175" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E175">
         <v>374921</v>
@@ -9393,16 +10443,22 @@
       <c r="P175">
         <v>0.02922421404728475</v>
       </c>
-    </row>
-    <row r="176" spans="1:16">
+      <c r="Q175">
+        <v>0.1559824845426453</v>
+      </c>
+      <c r="R175">
+        <v>0.1971133608412147</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18">
       <c r="A176" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C176" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D176">
         <v>5.313154220581055</v>
@@ -9443,16 +10499,22 @@
       <c r="P176">
         <v>0.02801557840559622</v>
       </c>
-    </row>
-    <row r="177" spans="1:16">
+      <c r="Q176">
+        <v>0.2438194258889443</v>
+      </c>
+      <c r="R176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18">
       <c r="A177" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B177" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C177" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D177">
         <v>7.007572650909424</v>
@@ -9493,25 +10555,31 @@
       <c r="P177">
         <v>0.01358474226114133</v>
       </c>
-    </row>
-    <row r="178" spans="1:16">
+      <c r="Q177">
+        <v>0.2366236273750927</v>
+      </c>
+      <c r="R177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18">
       <c r="A178" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B178" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C178" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D178">
-        <v>7.160837173461914</v>
+        <v>7.160837650299072</v>
       </c>
       <c r="E178">
         <v>2982810591</v>
       </c>
       <c r="F178">
-        <v>21359420961.4287</v>
+        <v>21359422383.74363</v>
       </c>
       <c r="G178">
         <v>451549</v>
@@ -9523,13 +10591,13 @@
         <v>23253055</v>
       </c>
       <c r="J178">
-        <v>21357217130.4287</v>
+        <v>21357218552.74363</v>
       </c>
       <c r="K178">
         <v>0.0214520497287691</v>
       </c>
       <c r="L178">
-        <v>2.114268901432179E-05</v>
+        <v>2.114268760629377E-05</v>
       </c>
       <c r="M178">
         <v>0.01897225977403829</v>
@@ -9543,25 +10611,31 @@
       <c r="P178">
         <v>0.0176397512746409</v>
       </c>
-    </row>
-    <row r="179" spans="1:16">
+      <c r="Q178">
+        <v>0.2216744990612202</v>
+      </c>
+      <c r="R178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18">
       <c r="A179" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B179" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C179" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D179">
-        <v>37.34615325927734</v>
+        <v>37.34616088867188</v>
       </c>
       <c r="E179">
         <v>4196212328</v>
       </c>
       <c r="F179">
-        <v>156712388709.957</v>
+        <v>156712420724.5164</v>
       </c>
       <c r="G179">
         <v>1538193</v>
@@ -9573,13 +10647,13 @@
         <v>14867453</v>
       </c>
       <c r="J179">
-        <v>156712008363.957</v>
+        <v>156712040378.5164</v>
       </c>
       <c r="K179">
         <v>0.1061766852415738</v>
       </c>
       <c r="L179">
-        <v>9.815412463016951E-06</v>
+        <v>9.815410457835318E-06</v>
       </c>
       <c r="M179">
         <v>0.08904961730835806</v>
@@ -9593,25 +10667,31 @@
       <c r="P179">
         <v>0.08748526346165143</v>
       </c>
-    </row>
-    <row r="180" spans="1:16">
+      <c r="Q179">
+        <v>0.5085576493115879</v>
+      </c>
+      <c r="R179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18">
       <c r="A180" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B180" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C180" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D180">
-        <v>34.82285308837891</v>
+        <v>34.82284545898438</v>
       </c>
       <c r="E180">
         <v>4196212328</v>
       </c>
       <c r="F180">
-        <v>146124085425.5884</v>
+        <v>146124053411.0291</v>
       </c>
       <c r="G180">
         <v>1681273</v>
@@ -9623,13 +10703,13 @@
         <v>15385027</v>
       </c>
       <c r="J180">
-        <v>146123719115.5884</v>
+        <v>146123687101.0291</v>
       </c>
       <c r="K180">
         <v>0.1119451814692294</v>
       </c>
       <c r="L180">
-        <v>1.150581856372038E-05</v>
+        <v>1.150582108455543E-05</v>
       </c>
       <c r="M180">
         <v>0.09163370334026713</v>
@@ -9643,25 +10723,31 @@
       <c r="P180">
         <v>0.08792875173202153</v>
       </c>
-    </row>
-    <row r="181" spans="1:16">
+      <c r="Q180">
+        <v>0.5096473037844764</v>
+      </c>
+      <c r="R180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18">
       <c r="A181" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B181" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C181" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D181">
-        <v>33.64117431640625</v>
+        <v>33.64117813110352</v>
       </c>
       <c r="E181">
         <v>4195234302</v>
       </c>
       <c r="F181">
-        <v>141132608451.7489</v>
+        <v>141132624455.2977</v>
       </c>
       <c r="G181">
         <v>1581169</v>
@@ -9673,13 +10759,13 @@
         <v>16123041</v>
       </c>
       <c r="J181">
-        <v>141131819491.7489</v>
+        <v>141131835495.2977</v>
       </c>
       <c r="K181">
         <v>0.1031146894293828</v>
       </c>
       <c r="L181">
-        <v>1.120349050762745E-05</v>
+        <v>1.120348923721524E-05</v>
       </c>
       <c r="M181">
         <v>0.08347631194388205</v>
@@ -9693,25 +10779,31 @@
       <c r="P181">
         <v>0.08197595694662201</v>
       </c>
-    </row>
-    <row r="182" spans="1:16">
+      <c r="Q181">
+        <v>0.4918243739192969</v>
+      </c>
+      <c r="R181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18">
       <c r="A182" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B182" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C182" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D182">
-        <v>1.776076793670654</v>
+        <v>1.776076912879944</v>
       </c>
       <c r="E182">
         <v>941137513</v>
       </c>
       <c r="F182">
-        <v>1671532496.492214</v>
+        <v>1671532608.684548</v>
       </c>
       <c r="G182">
         <v>258134</v>
@@ -9723,13 +10815,13 @@
         <v>3131093</v>
       </c>
       <c r="J182">
-        <v>1672290246.492214</v>
+        <v>1672290358.684548</v>
       </c>
       <c r="K182">
         <v>0.06637809754726534</v>
       </c>
       <c r="L182">
-        <v>0.0001543595679885477</v>
+        <v>0.0001543595576327143</v>
       </c>
       <c r="M182">
         <v>0.07546118879253985</v>
@@ -9743,25 +10835,31 @@
       <c r="P182">
         <v>0.04234852992837837</v>
       </c>
-    </row>
-    <row r="183" spans="1:16">
+      <c r="Q182">
+        <v>0.2964465203644889</v>
+      </c>
+      <c r="R182">
+        <v>0.2571361743008109</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18">
       <c r="A183" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B183" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C183" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D183">
-        <v>2.909862041473389</v>
+        <v>2.909862518310547</v>
       </c>
       <c r="E183">
         <v>941492372</v>
       </c>
       <c r="F183">
-        <v>2739612915.619543</v>
+        <v>2739613364.55809</v>
       </c>
       <c r="G183">
         <v>122019</v>
@@ -9773,13 +10871,13 @@
         <v>3250220</v>
       </c>
       <c r="J183">
-        <v>2740501534.619543</v>
+        <v>2740501983.55809</v>
       </c>
       <c r="K183">
         <v>0.02948145603151029</v>
       </c>
       <c r="L183">
-        <v>4.45243319365408E-05</v>
+        <v>4.452432464273513E-05</v>
       </c>
       <c r="M183">
         <v>0.04321430549316661</v>
@@ -9793,25 +10891,31 @@
       <c r="P183">
         <v>0.02506137946785429</v>
       </c>
-    </row>
-    <row r="184" spans="1:16">
+      <c r="Q183">
+        <v>0.2434616592440333</v>
+      </c>
+      <c r="R183">
+        <v>0.2683637018956264</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18">
       <c r="A184" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B184" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C184" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D184">
-        <v>3.296246528625488</v>
+        <v>3.296246290206909</v>
       </c>
       <c r="E184">
         <v>941492372</v>
       </c>
       <c r="F184">
-        <v>3103390962.932377</v>
+        <v>3103390738.463103</v>
       </c>
       <c r="G184">
         <v>176691</v>
@@ -9823,13 +10927,13 @@
         <v>3369746</v>
       </c>
       <c r="J184">
-        <v>3103872538.932377</v>
+        <v>3103872314.463103</v>
       </c>
       <c r="K184">
         <v>0.04587801279664489</v>
       </c>
       <c r="L184">
-        <v>5.692598448671333E-05</v>
+        <v>5.692598860354968E-05</v>
       </c>
       <c r="M184">
         <v>0.04798225148126892</v>
@@ -9843,25 +10947,31 @@
       <c r="P184">
         <v>0.02673449387615604</v>
       </c>
-    </row>
-    <row r="185" spans="1:16">
+      <c r="Q184">
+        <v>0.2670054830448235</v>
+      </c>
+      <c r="R184">
+        <v>0.251632752235191</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18">
       <c r="A185" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B185" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C185" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D185">
-        <v>15.22420883178711</v>
+        <v>15.22420787811279</v>
       </c>
       <c r="E185">
         <v>204325974</v>
       </c>
       <c r="F185">
-        <v>3110701297.934303</v>
+        <v>3110701103.07387</v>
       </c>
       <c r="G185">
         <v>973276</v>
@@ -9873,13 +10983,13 @@
         <v>5218264</v>
       </c>
       <c r="J185">
-        <v>3113584617.934303</v>
+        <v>3113584423.07387</v>
       </c>
       <c r="K185">
         <v>0.1201340379856581</v>
       </c>
       <c r="L185">
-        <v>0.0003125901876550625</v>
+        <v>0.0003125902072181934</v>
       </c>
       <c r="M185">
         <v>0.1101851113703714</v>
@@ -9893,16 +11003,22 @@
       <c r="P185">
         <v>0.03588152093091321</v>
       </c>
-    </row>
-    <row r="186" spans="1:16">
+      <c r="Q185">
+        <v>0.1918456790373849</v>
+      </c>
+      <c r="R185">
+        <v>0.2284257031445748</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18">
       <c r="A186" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B186" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C186" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D186">
         <v>14.93684482574463</v>
@@ -9943,16 +11059,22 @@
       <c r="P186">
         <v>0.02254546329113891</v>
       </c>
-    </row>
-    <row r="187" spans="1:16">
+      <c r="Q186">
+        <v>0.1377216771643581</v>
+      </c>
+      <c r="R186">
+        <v>0.2986361804648224</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18">
       <c r="A187" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B187" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C187" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D187">
         <v>15.3940954208374</v>
@@ -9993,25 +11115,31 @@
       <c r="P187">
         <v>0.01026542183677726</v>
       </c>
-    </row>
-    <row r="188" spans="1:16">
+      <c r="Q187">
+        <v>0.128918274852877</v>
+      </c>
+      <c r="R187">
+        <v>0.288640425051012</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18">
       <c r="A188" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B188" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C188" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D188">
-        <v>13.3056526184082</v>
+        <v>13.30565357208252</v>
       </c>
       <c r="E188">
         <v>5501851541</v>
       </c>
       <c r="F188">
-        <v>73205725362.59985</v>
+        <v>73205730609.57437</v>
       </c>
       <c r="G188">
         <v>1621395</v>
@@ -10023,13 +11151,13 @@
         <v>10668360</v>
       </c>
       <c r="J188">
-        <v>73229603257.59985</v>
+        <v>73229608504.57437</v>
       </c>
       <c r="K188">
         <v>0.0469340309101522</v>
       </c>
       <c r="L188">
-        <v>2.214125064007813E-05</v>
+        <v>2.214124905363543E-05</v>
       </c>
       <c r="M188">
         <v>0.1183055314968749</v>
@@ -10043,25 +11171,31 @@
       <c r="P188">
         <v>0.02711415886988641</v>
       </c>
-    </row>
-    <row r="189" spans="1:16">
+      <c r="Q188">
+        <v>0.1037788788254511</v>
+      </c>
+      <c r="R188">
+        <v>0.6039803349596266</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18">
       <c r="A189" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B189" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C189" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D189">
-        <v>16.30115509033203</v>
+        <v>16.30115127563477</v>
       </c>
       <c r="E189">
         <v>5517270006</v>
       </c>
       <c r="F189">
-        <v>89937874043.04314</v>
+        <v>89937852996.32834</v>
       </c>
       <c r="G189">
         <v>1127589</v>
@@ -10073,13 +11207,13 @@
         <v>11784278</v>
       </c>
       <c r="J189">
-        <v>89961117957.04314</v>
+        <v>89961096910.32834</v>
       </c>
       <c r="K189">
         <v>0.03219089926194307</v>
       </c>
       <c r="L189">
-        <v>1.253418171768862E-05</v>
+        <v>1.253418465010449E-05</v>
       </c>
       <c r="M189">
         <v>0.08237237784105229</v>
@@ -10093,25 +11227,31 @@
       <c r="P189">
         <v>0.02055842779182075</v>
       </c>
-    </row>
-    <row r="190" spans="1:16">
+      <c r="Q189">
+        <v>0.09091250265240419</v>
+      </c>
+      <c r="R189">
+        <v>0.5629551828989285</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18">
       <c r="A190" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B190" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C190" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D190">
-        <v>18.01548957824707</v>
+        <v>18.01548767089844</v>
       </c>
       <c r="E190">
         <v>5516675296</v>
       </c>
       <c r="F190">
-        <v>99385606301.66107</v>
+        <v>99385595779.43799</v>
       </c>
       <c r="G190">
         <v>634679</v>
@@ -10123,13 +11263,13 @@
         <v>11159889</v>
       </c>
       <c r="J190">
-        <v>99410091069.66107</v>
+        <v>99410080547.43799</v>
       </c>
       <c r="K190">
         <v>0.01780572611485643</v>
       </c>
       <c r="L190">
-        <v>6.384452455186388E-06</v>
+        <v>6.384453130959233E-06</v>
       </c>
       <c r="M190">
         <v>0.02191598859092595</v>
@@ -10143,25 +11283,31 @@
       <c r="P190">
         <v>0.005027031134439868</v>
       </c>
-    </row>
-    <row r="191" spans="1:16">
+      <c r="Q190">
+        <v>0.09044477468806582</v>
+      </c>
+      <c r="R190">
+        <v>0.591527185462117</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18">
       <c r="A191" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B191" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C191" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D191">
-        <v>7.090343952178955</v>
+        <v>7.090344905853271</v>
       </c>
       <c r="E191">
         <v>1032705804</v>
       </c>
       <c r="F191">
-        <v>7322239351.771505</v>
+        <v>7322240336.636507</v>
       </c>
       <c r="G191">
         <v>4288523</v>
@@ -10173,13 +11319,13 @@
         <v>17303231</v>
       </c>
       <c r="J191">
-        <v>7322239313.771505</v>
+        <v>7322240298.636507</v>
       </c>
       <c r="K191">
         <v>0.2478457588723653</v>
       </c>
       <c r="L191">
-        <v>0.0005856846268236878</v>
+        <v>0.0005856845480472113</v>
       </c>
       <c r="M191">
         <v>0.1870477831567989</v>
@@ -10193,25 +11339,31 @@
       <c r="P191">
         <v>0.1869312160358359</v>
       </c>
-    </row>
-    <row r="192" spans="1:16">
+      <c r="Q191">
+        <v>1.090001161486404</v>
+      </c>
+      <c r="R191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18">
       <c r="A192" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B192" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C192" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D192">
-        <v>7.277212619781494</v>
+        <v>7.277209758758545</v>
       </c>
       <c r="E192">
         <v>1032705804</v>
       </c>
       <c r="F192">
-        <v>7515219709.390394</v>
+        <v>7515216754.795389</v>
       </c>
       <c r="G192">
         <v>2852794</v>
@@ -10223,13 +11375,13 @@
         <v>17401663</v>
       </c>
       <c r="J192">
-        <v>7515219668.390394</v>
+        <v>7515216713.795389</v>
       </c>
       <c r="K192">
         <v>0.1639383960874452</v>
       </c>
       <c r="L192">
-        <v>0.0003796022106977227</v>
+        <v>0.0003796023599377032</v>
       </c>
       <c r="M192">
         <v>0.1225470232356528</v>
@@ -10243,25 +11395,31 @@
       <c r="P192">
         <v>0.1222414418116104</v>
       </c>
-    </row>
-    <row r="193" spans="1:16">
+      <c r="Q192">
+        <v>1.047016238998957</v>
+      </c>
+      <c r="R192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18">
       <c r="A193" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B193" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C193" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D193">
-        <v>7.016744613647461</v>
+        <v>7.016742706298828</v>
       </c>
       <c r="E193">
         <v>1032705804</v>
       </c>
       <c r="F193">
-        <v>7246232887.699471</v>
+        <v>7246230917.969467</v>
       </c>
       <c r="G193">
         <v>2380878</v>
@@ -10273,13 +11431,13 @@
         <v>17948083</v>
       </c>
       <c r="J193">
-        <v>7246232846.699471</v>
+        <v>7246230876.969467</v>
       </c>
       <c r="K193">
         <v>0.1326539128892165</v>
       </c>
       <c r="L193">
-        <v>0.0003285676917054146</v>
+        <v>0.0003285677810193836</v>
       </c>
       <c r="M193">
         <v>0.08987316361307221</v>
@@ -10293,16 +11451,22 @@
       <c r="P193">
         <v>0.08981575045619168</v>
       </c>
-    </row>
-    <row r="194" spans="1:16">
+      <c r="Q193">
+        <v>0.9500935323790856</v>
+      </c>
+      <c r="R193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18">
       <c r="A194" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B194" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C194" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D194">
         <v>12.99902057647705</v>
@@ -10343,16 +11507,22 @@
       <c r="P194">
         <v>0.003061236178828926</v>
       </c>
-    </row>
-    <row r="195" spans="1:16">
+      <c r="Q194">
+        <v>0.1816666868497303</v>
+      </c>
+      <c r="R194">
+        <v>0.06638776945617335</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18">
       <c r="A195" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B195" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C195" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D195">
         <v>15.82502269744873</v>
@@ -10393,25 +11563,31 @@
       <c r="P195">
         <v>0.01468367484117563</v>
       </c>
-    </row>
-    <row r="196" spans="1:16">
+      <c r="Q195">
+        <v>0.2240000669938669</v>
+      </c>
+      <c r="R195">
+        <v>0.06714786332714173</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18">
       <c r="A196" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B196" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C196" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D196">
-        <v>10.74954319000244</v>
+        <v>10.74954223632812</v>
       </c>
       <c r="E196">
         <v>955601</v>
       </c>
       <c r="F196">
-        <v>10272274.22190952</v>
+        <v>10272273.31057739</v>
       </c>
       <c r="G196">
         <v>91828</v>
@@ -10423,13 +11599,13 @@
         <v>9765091</v>
       </c>
       <c r="J196">
-        <v>8829881.221909523</v>
+        <v>8829880.310577393</v>
       </c>
       <c r="K196">
         <v>0.01103344131914915</v>
       </c>
       <c r="L196">
-        <v>0.01039968689184038</v>
+        <v>0.01039968796519228</v>
       </c>
       <c r="M196">
         <v>0.01770613299968224</v>
@@ -10442,6 +11618,12 @@
       </c>
       <c r="P196">
         <v>0.01094387452350548</v>
+      </c>
+      <c r="Q196">
+        <v>0.1960314514074489</v>
+      </c>
+      <c r="R196">
+        <v>0.06429195564902153</v>
       </c>
     </row>
   </sheetData>
